--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120173623</v>
+        <v>120173616</v>
       </c>
       <c r="B2" t="n">
-        <v>90907</v>
+        <v>79567</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2063</v>
+        <v>229497</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Forskulla, Ås lm</t>
+          <t>Storforsen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609988</v>
+        <v>609789</v>
       </c>
       <c r="R2" t="n">
-        <v>7130120</v>
+        <v>7130369</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120173616</v>
+        <v>120173623</v>
       </c>
       <c r="B3" t="n">
-        <v>79567</v>
+        <v>90907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>2063</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,14 +829,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storforsen, Ås lm</t>
+          <t>Forskulla, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609789</v>
+        <v>609988</v>
       </c>
       <c r="R3" t="n">
-        <v>7130369</v>
+        <v>7130120</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120173616</v>
+        <v>120173624</v>
       </c>
       <c r="B2" t="n">
-        <v>79567</v>
+        <v>91246</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>898</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609789</v>
+        <v>609777</v>
       </c>
       <c r="R2" t="n">
-        <v>7130369</v>
+        <v>7130284</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120173623</v>
+        <v>120173616</v>
       </c>
       <c r="B3" t="n">
-        <v>90907</v>
+        <v>79583</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2063</v>
+        <v>229497</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,14 +829,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Forskulla, Ås lm</t>
+          <t>Storforsen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609988</v>
+        <v>609789</v>
       </c>
       <c r="R3" t="n">
-        <v>7130120</v>
+        <v>7130369</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +908,7 @@
         <v>120173621</v>
       </c>
       <c r="B4" t="n">
-        <v>90763</v>
+        <v>90781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120173624</v>
+        <v>120173623</v>
       </c>
       <c r="B5" t="n">
-        <v>91228</v>
+        <v>90925</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>898</v>
+        <v>2063</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,14 +1059,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storforsen, Ås lm</t>
+          <t>Forskulla, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609777</v>
+        <v>609988</v>
       </c>
       <c r="R5" t="n">
-        <v>7130284</v>
+        <v>7130120</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120173624</v>
+        <v>120173623</v>
       </c>
       <c r="B2" t="n">
-        <v>91246</v>
+        <v>90925</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>898</v>
+        <v>2063</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storforsen, Ås lm</t>
+          <t>Forskulla, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609777</v>
+        <v>609988</v>
       </c>
       <c r="R2" t="n">
-        <v>7130284</v>
+        <v>7130120</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120173616</v>
+        <v>120173621</v>
       </c>
       <c r="B3" t="n">
-        <v>79583</v>
+        <v>90781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>1106</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609789</v>
+        <v>609979</v>
       </c>
       <c r="R3" t="n">
-        <v>7130369</v>
+        <v>7130165</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120173621</v>
+        <v>120173616</v>
       </c>
       <c r="B4" t="n">
-        <v>90781</v>
+        <v>79583</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,25 +917,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1106</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609979</v>
+        <v>609789</v>
       </c>
       <c r="R4" t="n">
-        <v>7130165</v>
+        <v>7130369</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120173623</v>
+        <v>120173624</v>
       </c>
       <c r="B5" t="n">
-        <v>90925</v>
+        <v>91246</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2063</v>
+        <v>898</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,14 +1059,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Forskulla, Ås lm</t>
+          <t>Storforsen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609988</v>
+        <v>609777</v>
       </c>
       <c r="R5" t="n">
-        <v>7130120</v>
+        <v>7130284</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120173623</v>
+        <v>120173624</v>
       </c>
       <c r="B2" t="n">
-        <v>90925</v>
+        <v>91246</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2063</v>
+        <v>898</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Forskulla, Ås lm</t>
+          <t>Storforsen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609988</v>
+        <v>609777</v>
       </c>
       <c r="R2" t="n">
-        <v>7130120</v>
+        <v>7130284</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120173621</v>
+        <v>120173616</v>
       </c>
       <c r="B3" t="n">
-        <v>90781</v>
+        <v>79583</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1106</v>
+        <v>229497</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609979</v>
+        <v>609789</v>
       </c>
       <c r="R3" t="n">
-        <v>7130165</v>
+        <v>7130369</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120173616</v>
+        <v>120173621</v>
       </c>
       <c r="B4" t="n">
-        <v>79583</v>
+        <v>90781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,25 +917,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>1106</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609789</v>
+        <v>609979</v>
       </c>
       <c r="R4" t="n">
-        <v>7130369</v>
+        <v>7130165</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120173624</v>
+        <v>120173623</v>
       </c>
       <c r="B5" t="n">
-        <v>91246</v>
+        <v>90925</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>898</v>
+        <v>2063</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,14 +1059,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storforsen, Ås lm</t>
+          <t>Forskulla, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609777</v>
+        <v>609988</v>
       </c>
       <c r="R5" t="n">
-        <v>7130284</v>
+        <v>7130120</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120173624</v>
+        <v>120173621</v>
       </c>
       <c r="B2" t="n">
-        <v>91246</v>
+        <v>90781</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>898</v>
+        <v>1106</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609777</v>
+        <v>609979</v>
       </c>
       <c r="R2" t="n">
-        <v>7130284</v>
+        <v>7130165</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120173616</v>
+        <v>120173624</v>
       </c>
       <c r="B3" t="n">
-        <v>79583</v>
+        <v>91246</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>898</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609789</v>
+        <v>609777</v>
       </c>
       <c r="R3" t="n">
-        <v>7130369</v>
+        <v>7130284</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120173621</v>
+        <v>120173616</v>
       </c>
       <c r="B4" t="n">
-        <v>90781</v>
+        <v>79583</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,25 +917,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1106</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609979</v>
+        <v>609789</v>
       </c>
       <c r="R4" t="n">
-        <v>7130165</v>
+        <v>7130369</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120173621</v>
+        <v>120173623</v>
       </c>
       <c r="B2" t="n">
-        <v>90781</v>
+        <v>90925</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1106</v>
+        <v>2063</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storforsen, Ås lm</t>
+          <t>Forskulla, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609979</v>
+        <v>609988</v>
       </c>
       <c r="R2" t="n">
-        <v>7130165</v>
+        <v>7130120</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120173616</v>
+        <v>120173621</v>
       </c>
       <c r="B4" t="n">
-        <v>79583</v>
+        <v>90781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,25 +917,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>1106</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609789</v>
+        <v>609979</v>
       </c>
       <c r="R4" t="n">
-        <v>7130369</v>
+        <v>7130165</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120173623</v>
+        <v>120173616</v>
       </c>
       <c r="B5" t="n">
-        <v>90925</v>
+        <v>79583</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2063</v>
+        <v>229497</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,14 +1059,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Forskulla, Ås lm</t>
+          <t>Storforsen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609988</v>
+        <v>609789</v>
       </c>
       <c r="R5" t="n">
-        <v>7130120</v>
+        <v>7130369</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120173623</v>
+        <v>120173624</v>
       </c>
       <c r="B2" t="n">
-        <v>90925</v>
+        <v>91246</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2063</v>
+        <v>898</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Forskulla, Ås lm</t>
+          <t>Storforsen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609988</v>
+        <v>609777</v>
       </c>
       <c r="R2" t="n">
-        <v>7130120</v>
+        <v>7130284</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120173624</v>
+        <v>120173621</v>
       </c>
       <c r="B3" t="n">
-        <v>91246</v>
+        <v>90781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>898</v>
+        <v>1106</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609777</v>
+        <v>609979</v>
       </c>
       <c r="R3" t="n">
-        <v>7130284</v>
+        <v>7130165</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120173621</v>
+        <v>120173623</v>
       </c>
       <c r="B4" t="n">
-        <v>90781</v>
+        <v>90925</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1106</v>
+        <v>2063</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,14 +944,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storforsen, Ås lm</t>
+          <t>Forskulla, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609979</v>
+        <v>609988</v>
       </c>
       <c r="R4" t="n">
-        <v>7130165</v>
+        <v>7130120</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1133,6 +1133,2868 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121492772</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>609974</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7130178</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121492770</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90914</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>609984</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7130168</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121492740</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90728</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>609775</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7130324</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121492759</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>609921</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7130257</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121492726</v>
+      </c>
+      <c r="B10" t="n">
+        <v>74710</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>610001</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7130079</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121492737</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91366</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>898</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>609780</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7130283</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121492757</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>609889</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7130269</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121492771</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>609982</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7130159</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121492756</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>609843</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7130300</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121492747</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57242</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Accipiter gentilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>609772</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7130374</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121492768</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57720</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>609981</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7130120</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121492761</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>609958</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7130181</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121492749</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>609806</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7130354</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121492769</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57504</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>609981</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7130145</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121492764</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90728</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>609989</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7130116</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121492738</v>
+      </c>
+      <c r="B21" t="n">
+        <v>90710</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>609790</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7130308</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121492758</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>609901</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7130280</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121492754</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>609790</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7130365</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121492763</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91056</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2063</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Grantickeporing</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Skeletocutis chrysella</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>609987</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7130117</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121492739</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97049</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>609783</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7130330</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121492733</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80561</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>609965</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7130082</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121492751</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79645</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>609793</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7130371</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121492753</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>609794</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7130370</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121492752</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79714</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>609792</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7130369</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121492755</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90710</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>609807</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7130345</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121492762</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90728</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>609986</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7130123</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121492746</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>609772</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7130393</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121492772</v>
+        <v>121492752</v>
       </c>
       <c r="B6" t="n">
-        <v>78604</v>
+        <v>79714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,25 +1147,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609974</v>
+        <v>609792</v>
       </c>
       <c r="R6" t="n">
-        <v>7130178</v>
+        <v>7130369</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121492770</v>
+        <v>121492759</v>
       </c>
       <c r="B7" t="n">
-        <v>90914</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,25 +1253,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1106</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609984</v>
+        <v>609921</v>
       </c>
       <c r="R7" t="n">
-        <v>7130168</v>
+        <v>7130257</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121492740</v>
+        <v>121492768</v>
       </c>
       <c r="B8" t="n">
-        <v>90728</v>
+        <v>57720</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609775</v>
+        <v>609981</v>
       </c>
       <c r="R8" t="n">
-        <v>7130324</v>
+        <v>7130120</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,7 +1453,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121492759</v>
+        <v>121492772</v>
       </c>
       <c r="B9" t="n">
         <v>78604</v>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609921</v>
+        <v>609974</v>
       </c>
       <c r="R9" t="n">
-        <v>7130257</v>
+        <v>7130178</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121492726</v>
+        <v>121492763</v>
       </c>
       <c r="B10" t="n">
-        <v>74710</v>
+        <v>91056</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,25 +1571,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>2063</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610001</v>
+        <v>609987</v>
       </c>
       <c r="R10" t="n">
-        <v>7130079</v>
+        <v>7130117</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121492737</v>
+        <v>121492769</v>
       </c>
       <c r="B11" t="n">
-        <v>91366</v>
+        <v>57504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,25 +1677,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>898</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609780</v>
+        <v>609981</v>
       </c>
       <c r="R11" t="n">
-        <v>7130283</v>
+        <v>7130145</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121492757</v>
+        <v>121492739</v>
       </c>
       <c r="B12" t="n">
-        <v>78604</v>
+        <v>97049</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1783,25 +1783,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609889</v>
+        <v>609783</v>
       </c>
       <c r="R12" t="n">
-        <v>7130269</v>
+        <v>7130330</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121492771</v>
+        <v>121492758</v>
       </c>
       <c r="B13" t="n">
         <v>78604</v>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609982</v>
+        <v>609901</v>
       </c>
       <c r="R13" t="n">
-        <v>7130159</v>
+        <v>7130280</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121492756</v>
+        <v>121492757</v>
       </c>
       <c r="B14" t="n">
-        <v>5189</v>
+        <v>78604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,25 +1995,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609843</v>
+        <v>609889</v>
       </c>
       <c r="R14" t="n">
-        <v>7130300</v>
+        <v>7130269</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121492747</v>
+        <v>121492770</v>
       </c>
       <c r="B15" t="n">
-        <v>57242</v>
+        <v>90914</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,25 +2101,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100001</v>
+        <v>1106</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609772</v>
+        <v>609984</v>
       </c>
       <c r="R15" t="n">
-        <v>7130374</v>
+        <v>7130168</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121492768</v>
+        <v>121492753</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>79685</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2207,25 +2207,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609981</v>
+        <v>609794</v>
       </c>
       <c r="R16" t="n">
-        <v>7130120</v>
+        <v>7130370</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121492761</v>
+        <v>121492738</v>
       </c>
       <c r="B17" t="n">
-        <v>57367</v>
+        <v>90710</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2317,21 +2317,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609958</v>
+        <v>609790</v>
       </c>
       <c r="R17" t="n">
-        <v>7130181</v>
+        <v>7130308</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121492749</v>
+        <v>121492755</v>
       </c>
       <c r="B18" t="n">
-        <v>78604</v>
+        <v>90710</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,21 +2423,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609806</v>
+        <v>609807</v>
       </c>
       <c r="R18" t="n">
-        <v>7130354</v>
+        <v>7130345</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121492769</v>
+        <v>121492733</v>
       </c>
       <c r="B19" t="n">
-        <v>57504</v>
+        <v>80561</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2529,21 +2529,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>1049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609981</v>
+        <v>609965</v>
       </c>
       <c r="R19" t="n">
-        <v>7130145</v>
+        <v>7130082</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121492764</v>
+        <v>121492726</v>
       </c>
       <c r="B20" t="n">
-        <v>90728</v>
+        <v>74710</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2635,21 +2635,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609989</v>
+        <v>610001</v>
       </c>
       <c r="R20" t="n">
-        <v>7130116</v>
+        <v>7130079</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121492738</v>
+        <v>121492771</v>
       </c>
       <c r="B21" t="n">
-        <v>90710</v>
+        <v>78604</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609790</v>
+        <v>609982</v>
       </c>
       <c r="R21" t="n">
-        <v>7130308</v>
+        <v>7130159</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2831,10 +2831,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121492758</v>
+        <v>121492747</v>
       </c>
       <c r="B22" t="n">
-        <v>78604</v>
+        <v>57242</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2847,21 +2847,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100001</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609901</v>
+        <v>609772</v>
       </c>
       <c r="R22" t="n">
-        <v>7130280</v>
+        <v>7130374</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121492754</v>
+        <v>121492749</v>
       </c>
       <c r="B23" t="n">
         <v>78604</v>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609790</v>
+        <v>609806</v>
       </c>
       <c r="R23" t="n">
-        <v>7130365</v>
+        <v>7130354</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121492763</v>
+        <v>121492751</v>
       </c>
       <c r="B24" t="n">
-        <v>91056</v>
+        <v>79645</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3055,25 +3055,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2063</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609987</v>
+        <v>609793</v>
       </c>
       <c r="R24" t="n">
-        <v>7130117</v>
+        <v>7130371</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3149,10 +3149,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121492739</v>
+        <v>121492754</v>
       </c>
       <c r="B25" t="n">
-        <v>97049</v>
+        <v>78604</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3161,25 +3161,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609783</v>
+        <v>609790</v>
       </c>
       <c r="R25" t="n">
-        <v>7130330</v>
+        <v>7130365</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121492733</v>
+        <v>121492740</v>
       </c>
       <c r="B26" t="n">
-        <v>80561</v>
+        <v>90728</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1049</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609965</v>
+        <v>609775</v>
       </c>
       <c r="R26" t="n">
-        <v>7130082</v>
+        <v>7130324</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121492751</v>
+        <v>121492761</v>
       </c>
       <c r="B27" t="n">
-        <v>79645</v>
+        <v>57367</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3373,25 +3373,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609793</v>
+        <v>609958</v>
       </c>
       <c r="R27" t="n">
-        <v>7130371</v>
+        <v>7130181</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121492753</v>
+        <v>121492762</v>
       </c>
       <c r="B28" t="n">
-        <v>79685</v>
+        <v>90728</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3483,21 +3483,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609794</v>
+        <v>609986</v>
       </c>
       <c r="R28" t="n">
-        <v>7130370</v>
+        <v>7130123</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121492752</v>
+        <v>121492746</v>
       </c>
       <c r="B29" t="n">
-        <v>79714</v>
+        <v>78604</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3585,25 +3585,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609792</v>
+        <v>609772</v>
       </c>
       <c r="R29" t="n">
-        <v>7130369</v>
+        <v>7130393</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,10 +3679,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121492755</v>
+        <v>121492737</v>
       </c>
       <c r="B30" t="n">
-        <v>90710</v>
+        <v>91366</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3691,25 +3691,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609807</v>
+        <v>609780</v>
       </c>
       <c r="R30" t="n">
-        <v>7130345</v>
+        <v>7130283</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,7 +3785,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121492762</v>
+        <v>121492764</v>
       </c>
       <c r="B31" t="n">
         <v>90728</v>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609986</v>
+        <v>609989</v>
       </c>
       <c r="R31" t="n">
-        <v>7130123</v>
+        <v>7130116</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121492746</v>
+        <v>121492756</v>
       </c>
       <c r="B32" t="n">
-        <v>78604</v>
+        <v>5189</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3903,25 +3903,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609772</v>
+        <v>609843</v>
       </c>
       <c r="R32" t="n">
-        <v>7130393</v>
+        <v>7130300</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121492752</v>
+        <v>121492757</v>
       </c>
       <c r="B6" t="n">
-        <v>79714</v>
+        <v>78607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,25 +1147,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609792</v>
+        <v>609889</v>
       </c>
       <c r="R6" t="n">
-        <v>7130369</v>
+        <v>7130269</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121492759</v>
+        <v>121492752</v>
       </c>
       <c r="B7" t="n">
-        <v>78604</v>
+        <v>79717</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,25 +1253,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609921</v>
+        <v>609792</v>
       </c>
       <c r="R7" t="n">
-        <v>7130257</v>
+        <v>7130369</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121492768</v>
+        <v>121492763</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>91059</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>2063</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609981</v>
+        <v>609987</v>
       </c>
       <c r="R8" t="n">
-        <v>7130120</v>
+        <v>7130117</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121492772</v>
+        <v>121492738</v>
       </c>
       <c r="B9" t="n">
-        <v>78604</v>
+        <v>90713</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,21 +1469,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609974</v>
+        <v>609790</v>
       </c>
       <c r="R9" t="n">
-        <v>7130178</v>
+        <v>7130308</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121492763</v>
+        <v>121492737</v>
       </c>
       <c r="B10" t="n">
-        <v>91056</v>
+        <v>91369</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2063</v>
+        <v>898</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609987</v>
+        <v>609780</v>
       </c>
       <c r="R10" t="n">
-        <v>7130117</v>
+        <v>7130283</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121492769</v>
+        <v>121492758</v>
       </c>
       <c r="B11" t="n">
-        <v>57504</v>
+        <v>78607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609981</v>
+        <v>609901</v>
       </c>
       <c r="R11" t="n">
-        <v>7130145</v>
+        <v>7130280</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121492739</v>
+        <v>121492772</v>
       </c>
       <c r="B12" t="n">
-        <v>97049</v>
+        <v>78607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1783,25 +1783,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609783</v>
+        <v>609974</v>
       </c>
       <c r="R12" t="n">
-        <v>7130330</v>
+        <v>7130178</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121492758</v>
+        <v>121492756</v>
       </c>
       <c r="B13" t="n">
-        <v>78604</v>
+        <v>5192</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1889,25 +1889,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609901</v>
+        <v>609843</v>
       </c>
       <c r="R13" t="n">
-        <v>7130280</v>
+        <v>7130300</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121492757</v>
+        <v>121492754</v>
       </c>
       <c r="B14" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609889</v>
+        <v>609790</v>
       </c>
       <c r="R14" t="n">
-        <v>7130269</v>
+        <v>7130365</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121492770</v>
+        <v>121492740</v>
       </c>
       <c r="B15" t="n">
-        <v>90914</v>
+        <v>90731</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,25 +2101,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1106</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609984</v>
+        <v>609775</v>
       </c>
       <c r="R15" t="n">
-        <v>7130168</v>
+        <v>7130324</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121492753</v>
+        <v>121492746</v>
       </c>
       <c r="B16" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609794</v>
+        <v>609772</v>
       </c>
       <c r="R16" t="n">
-        <v>7130370</v>
+        <v>7130393</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121492738</v>
+        <v>121492770</v>
       </c>
       <c r="B17" t="n">
-        <v>90710</v>
+        <v>90917</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2313,25 +2313,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1106</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609790</v>
+        <v>609984</v>
       </c>
       <c r="R17" t="n">
-        <v>7130308</v>
+        <v>7130168</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121492755</v>
+        <v>121492747</v>
       </c>
       <c r="B18" t="n">
-        <v>90710</v>
+        <v>57245</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,21 +2423,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609807</v>
+        <v>609772</v>
       </c>
       <c r="R18" t="n">
-        <v>7130345</v>
+        <v>7130374</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121492733</v>
+        <v>121492761</v>
       </c>
       <c r="B19" t="n">
-        <v>80561</v>
+        <v>57370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2529,21 +2529,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609965</v>
+        <v>609958</v>
       </c>
       <c r="R19" t="n">
-        <v>7130082</v>
+        <v>7130181</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121492726</v>
+        <v>121492759</v>
       </c>
       <c r="B20" t="n">
-        <v>74710</v>
+        <v>78607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2635,21 +2635,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>610001</v>
+        <v>609921</v>
       </c>
       <c r="R20" t="n">
-        <v>7130079</v>
+        <v>7130257</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121492771</v>
+        <v>121492739</v>
       </c>
       <c r="B21" t="n">
-        <v>78604</v>
+        <v>97052</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2737,25 +2737,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609982</v>
+        <v>609783</v>
       </c>
       <c r="R21" t="n">
-        <v>7130159</v>
+        <v>7130330</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2831,10 +2831,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121492747</v>
+        <v>121492769</v>
       </c>
       <c r="B22" t="n">
-        <v>57242</v>
+        <v>57507</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2847,21 +2847,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100001</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609772</v>
+        <v>609981</v>
       </c>
       <c r="R22" t="n">
-        <v>7130374</v>
+        <v>7130145</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121492749</v>
+        <v>121492764</v>
       </c>
       <c r="B23" t="n">
-        <v>78604</v>
+        <v>90731</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2953,21 +2953,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609806</v>
+        <v>609989</v>
       </c>
       <c r="R23" t="n">
-        <v>7130354</v>
+        <v>7130116</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121492751</v>
+        <v>121492753</v>
       </c>
       <c r="B24" t="n">
-        <v>79645</v>
+        <v>79688</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3055,25 +3055,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609793</v>
+        <v>609794</v>
       </c>
       <c r="R24" t="n">
-        <v>7130371</v>
+        <v>7130370</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3149,10 +3149,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121492754</v>
+        <v>121492762</v>
       </c>
       <c r="B25" t="n">
-        <v>78604</v>
+        <v>90731</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3165,21 +3165,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609790</v>
+        <v>609986</v>
       </c>
       <c r="R25" t="n">
-        <v>7130365</v>
+        <v>7130123</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121492740</v>
+        <v>121492726</v>
       </c>
       <c r="B26" t="n">
-        <v>90728</v>
+        <v>74713</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609775</v>
+        <v>610001</v>
       </c>
       <c r="R26" t="n">
-        <v>7130324</v>
+        <v>7130079</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121492761</v>
+        <v>121492755</v>
       </c>
       <c r="B27" t="n">
-        <v>57367</v>
+        <v>90713</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3377,21 +3377,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609958</v>
+        <v>609807</v>
       </c>
       <c r="R27" t="n">
-        <v>7130181</v>
+        <v>7130345</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121492762</v>
+        <v>121492733</v>
       </c>
       <c r="B28" t="n">
-        <v>90728</v>
+        <v>80564</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3483,21 +3483,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609986</v>
+        <v>609965</v>
       </c>
       <c r="R28" t="n">
-        <v>7130123</v>
+        <v>7130082</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121492746</v>
+        <v>121492751</v>
       </c>
       <c r="B29" t="n">
-        <v>78604</v>
+        <v>79648</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3585,25 +3585,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609772</v>
+        <v>609793</v>
       </c>
       <c r="R29" t="n">
-        <v>7130393</v>
+        <v>7130371</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,10 +3679,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121492737</v>
+        <v>121492768</v>
       </c>
       <c r="B30" t="n">
-        <v>91366</v>
+        <v>57723</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3691,25 +3691,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>898</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609780</v>
+        <v>609981</v>
       </c>
       <c r="R30" t="n">
-        <v>7130283</v>
+        <v>7130120</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121492764</v>
+        <v>121492749</v>
       </c>
       <c r="B31" t="n">
-        <v>90728</v>
+        <v>78607</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3801,21 +3801,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609989</v>
+        <v>609806</v>
       </c>
       <c r="R31" t="n">
-        <v>7130116</v>
+        <v>7130354</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121492756</v>
+        <v>121492771</v>
       </c>
       <c r="B32" t="n">
-        <v>5189</v>
+        <v>78607</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3903,25 +3903,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609843</v>
+        <v>609982</v>
       </c>
       <c r="R32" t="n">
-        <v>7130300</v>
+        <v>7130159</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121492757</v>
+        <v>121492764</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1151,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609889</v>
+        <v>609989</v>
       </c>
       <c r="R6" t="n">
-        <v>7130269</v>
+        <v>7130116</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121492752</v>
+        <v>121492747</v>
       </c>
       <c r="B7" t="n">
-        <v>79717</v>
+        <v>57245</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,25 +1253,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>100001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609792</v>
+        <v>609772</v>
       </c>
       <c r="R7" t="n">
-        <v>7130369</v>
+        <v>7130374</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121492763</v>
+        <v>121492740</v>
       </c>
       <c r="B8" t="n">
-        <v>91059</v>
+        <v>90731</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2063</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609987</v>
+        <v>609775</v>
       </c>
       <c r="R8" t="n">
-        <v>7130117</v>
+        <v>7130324</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121492737</v>
+        <v>121492761</v>
       </c>
       <c r="B10" t="n">
-        <v>91369</v>
+        <v>57370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,25 +1571,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>898</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609780</v>
+        <v>609958</v>
       </c>
       <c r="R10" t="n">
-        <v>7130283</v>
+        <v>7130181</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121492758</v>
+        <v>121492751</v>
       </c>
       <c r="B11" t="n">
-        <v>78607</v>
+        <v>79648</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,25 +1677,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609901</v>
+        <v>609793</v>
       </c>
       <c r="R11" t="n">
-        <v>7130280</v>
+        <v>7130371</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121492772</v>
+        <v>121492769</v>
       </c>
       <c r="B12" t="n">
-        <v>78607</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,21 +1787,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609974</v>
+        <v>609981</v>
       </c>
       <c r="R12" t="n">
-        <v>7130178</v>
+        <v>7130145</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121492756</v>
+        <v>121492754</v>
       </c>
       <c r="B13" t="n">
-        <v>5192</v>
+        <v>78607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1889,25 +1889,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609843</v>
+        <v>609790</v>
       </c>
       <c r="R13" t="n">
-        <v>7130300</v>
+        <v>7130365</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121492754</v>
+        <v>121492726</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>74713</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,21 +1999,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609790</v>
+        <v>610001</v>
       </c>
       <c r="R14" t="n">
-        <v>7130365</v>
+        <v>7130079</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121492740</v>
+        <v>121492739</v>
       </c>
       <c r="B15" t="n">
-        <v>90731</v>
+        <v>97052</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,25 +2101,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609775</v>
+        <v>609783</v>
       </c>
       <c r="R15" t="n">
-        <v>7130324</v>
+        <v>7130330</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,7 +2195,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121492746</v>
+        <v>121492772</v>
       </c>
       <c r="B16" t="n">
         <v>78607</v>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609772</v>
+        <v>609974</v>
       </c>
       <c r="R16" t="n">
-        <v>7130393</v>
+        <v>7130178</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121492770</v>
+        <v>121492733</v>
       </c>
       <c r="B17" t="n">
-        <v>90917</v>
+        <v>80564</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2313,25 +2313,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1106</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609984</v>
+        <v>609965</v>
       </c>
       <c r="R17" t="n">
-        <v>7130168</v>
+        <v>7130082</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121492747</v>
+        <v>121492737</v>
       </c>
       <c r="B18" t="n">
-        <v>57245</v>
+        <v>91369</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2419,25 +2419,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100001</v>
+        <v>898</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609772</v>
+        <v>609780</v>
       </c>
       <c r="R18" t="n">
-        <v>7130374</v>
+        <v>7130283</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121492761</v>
+        <v>121492770</v>
       </c>
       <c r="B19" t="n">
-        <v>57370</v>
+        <v>90917</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,25 +2525,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1106</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609958</v>
+        <v>609984</v>
       </c>
       <c r="R19" t="n">
-        <v>7130181</v>
+        <v>7130168</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121492759</v>
+        <v>121492756</v>
       </c>
       <c r="B20" t="n">
-        <v>78607</v>
+        <v>5192</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,25 +2631,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609921</v>
+        <v>609843</v>
       </c>
       <c r="R20" t="n">
-        <v>7130257</v>
+        <v>7130300</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121492739</v>
+        <v>121492752</v>
       </c>
       <c r="B21" t="n">
-        <v>97052</v>
+        <v>79717</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609783</v>
+        <v>609792</v>
       </c>
       <c r="R21" t="n">
-        <v>7130330</v>
+        <v>7130369</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2831,10 +2831,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121492769</v>
+        <v>121492755</v>
       </c>
       <c r="B22" t="n">
-        <v>57507</v>
+        <v>90713</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2847,21 +2847,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609981</v>
+        <v>609807</v>
       </c>
       <c r="R22" t="n">
-        <v>7130145</v>
+        <v>7130345</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121492764</v>
+        <v>121492757</v>
       </c>
       <c r="B23" t="n">
-        <v>90731</v>
+        <v>78607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2953,21 +2953,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609989</v>
+        <v>609889</v>
       </c>
       <c r="R23" t="n">
-        <v>7130116</v>
+        <v>7130269</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121492753</v>
+        <v>121492763</v>
       </c>
       <c r="B24" t="n">
-        <v>79688</v>
+        <v>91059</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3055,25 +3055,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>2063</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609794</v>
+        <v>609987</v>
       </c>
       <c r="R24" t="n">
-        <v>7130370</v>
+        <v>7130117</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3149,10 +3149,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121492762</v>
+        <v>121492771</v>
       </c>
       <c r="B25" t="n">
-        <v>90731</v>
+        <v>78607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3165,21 +3165,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609986</v>
+        <v>609982</v>
       </c>
       <c r="R25" t="n">
-        <v>7130123</v>
+        <v>7130159</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121492726</v>
+        <v>121492749</v>
       </c>
       <c r="B26" t="n">
-        <v>74713</v>
+        <v>78607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>610001</v>
+        <v>609806</v>
       </c>
       <c r="R26" t="n">
-        <v>7130079</v>
+        <v>7130354</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121492755</v>
+        <v>121492762</v>
       </c>
       <c r="B27" t="n">
-        <v>90713</v>
+        <v>90731</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3377,21 +3377,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609807</v>
+        <v>609986</v>
       </c>
       <c r="R27" t="n">
-        <v>7130345</v>
+        <v>7130123</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121492733</v>
+        <v>121492768</v>
       </c>
       <c r="B28" t="n">
-        <v>80564</v>
+        <v>57723</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3479,25 +3479,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609965</v>
+        <v>609981</v>
       </c>
       <c r="R28" t="n">
-        <v>7130082</v>
+        <v>7130120</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121492751</v>
+        <v>121492746</v>
       </c>
       <c r="B29" t="n">
-        <v>79648</v>
+        <v>78607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3585,25 +3585,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609793</v>
+        <v>609772</v>
       </c>
       <c r="R29" t="n">
-        <v>7130371</v>
+        <v>7130393</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,10 +3679,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121492768</v>
+        <v>121492753</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>79688</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3691,25 +3691,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609981</v>
+        <v>609794</v>
       </c>
       <c r="R30" t="n">
-        <v>7130120</v>
+        <v>7130370</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,7 +3785,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121492749</v>
+        <v>121492759</v>
       </c>
       <c r="B31" t="n">
         <v>78607</v>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609806</v>
+        <v>609921</v>
       </c>
       <c r="R31" t="n">
-        <v>7130354</v>
+        <v>7130257</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3891,7 +3891,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121492771</v>
+        <v>121492758</v>
       </c>
       <c r="B32" t="n">
         <v>78607</v>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609982</v>
+        <v>609901</v>
       </c>
       <c r="R32" t="n">
-        <v>7130159</v>
+        <v>7130280</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -1241,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121492747</v>
+        <v>121492740</v>
       </c>
       <c r="B7" t="n">
-        <v>57245</v>
+        <v>90731</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,21 +1257,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100001</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609772</v>
+        <v>609775</v>
       </c>
       <c r="R7" t="n">
-        <v>7130374</v>
+        <v>7130324</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121492740</v>
+        <v>121492747</v>
       </c>
       <c r="B8" t="n">
-        <v>90731</v>
+        <v>57245</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609775</v>
+        <v>609772</v>
       </c>
       <c r="R8" t="n">
-        <v>7130324</v>
+        <v>7130374</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121492754</v>
+        <v>121492739</v>
       </c>
       <c r="B13" t="n">
-        <v>78607</v>
+        <v>97052</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1889,25 +1889,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609790</v>
+        <v>609783</v>
       </c>
       <c r="R13" t="n">
-        <v>7130365</v>
+        <v>7130330</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121492726</v>
+        <v>121492754</v>
       </c>
       <c r="B14" t="n">
-        <v>74713</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,21 +1999,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>610001</v>
+        <v>609790</v>
       </c>
       <c r="R14" t="n">
-        <v>7130079</v>
+        <v>7130365</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121492739</v>
+        <v>121492726</v>
       </c>
       <c r="B15" t="n">
-        <v>97052</v>
+        <v>74713</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,25 +2101,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609783</v>
+        <v>610001</v>
       </c>
       <c r="R15" t="n">
-        <v>7130330</v>
+        <v>7130079</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121492772</v>
+        <v>121492733</v>
       </c>
       <c r="B16" t="n">
-        <v>78607</v>
+        <v>80564</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609974</v>
+        <v>609965</v>
       </c>
       <c r="R16" t="n">
-        <v>7130178</v>
+        <v>7130082</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121492733</v>
+        <v>121492737</v>
       </c>
       <c r="B17" t="n">
-        <v>80564</v>
+        <v>91369</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2313,25 +2313,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1049</v>
+        <v>898</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609965</v>
+        <v>609780</v>
       </c>
       <c r="R17" t="n">
-        <v>7130082</v>
+        <v>7130283</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121492737</v>
+        <v>121492770</v>
       </c>
       <c r="B18" t="n">
-        <v>91369</v>
+        <v>90917</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,21 +2423,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>898</v>
+        <v>1106</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609780</v>
+        <v>609984</v>
       </c>
       <c r="R18" t="n">
-        <v>7130283</v>
+        <v>7130168</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121492770</v>
+        <v>121492772</v>
       </c>
       <c r="B19" t="n">
-        <v>90917</v>
+        <v>78607</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,25 +2525,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1106</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609984</v>
+        <v>609974</v>
       </c>
       <c r="R19" t="n">
-        <v>7130168</v>
+        <v>7130178</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121492756</v>
+        <v>121492752</v>
       </c>
       <c r="B20" t="n">
-        <v>5192</v>
+        <v>79717</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2635,21 +2635,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609843</v>
+        <v>609792</v>
       </c>
       <c r="R20" t="n">
-        <v>7130300</v>
+        <v>7130369</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121492752</v>
+        <v>121492756</v>
       </c>
       <c r="B21" t="n">
-        <v>79717</v>
+        <v>5192</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609792</v>
+        <v>609843</v>
       </c>
       <c r="R21" t="n">
-        <v>7130369</v>
+        <v>7130300</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2831,10 +2831,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121492755</v>
+        <v>121492757</v>
       </c>
       <c r="B22" t="n">
-        <v>90713</v>
+        <v>78607</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2847,21 +2847,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609807</v>
+        <v>609889</v>
       </c>
       <c r="R22" t="n">
-        <v>7130345</v>
+        <v>7130269</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121492757</v>
+        <v>121492755</v>
       </c>
       <c r="B23" t="n">
-        <v>78607</v>
+        <v>90713</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2953,21 +2953,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609889</v>
+        <v>609807</v>
       </c>
       <c r="R23" t="n">
-        <v>7130269</v>
+        <v>7130345</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121492733</v>
+        <v>121492772</v>
       </c>
       <c r="B16" t="n">
-        <v>80564</v>
+        <v>78607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609965</v>
+        <v>609974</v>
       </c>
       <c r="R16" t="n">
-        <v>7130082</v>
+        <v>7130178</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121492737</v>
+        <v>121492733</v>
       </c>
       <c r="B17" t="n">
-        <v>91369</v>
+        <v>80564</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2313,25 +2313,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>898</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609780</v>
+        <v>609965</v>
       </c>
       <c r="R17" t="n">
-        <v>7130283</v>
+        <v>7130082</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121492770</v>
+        <v>121492737</v>
       </c>
       <c r="B18" t="n">
-        <v>90917</v>
+        <v>91369</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,21 +2423,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1106</v>
+        <v>898</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609984</v>
+        <v>609780</v>
       </c>
       <c r="R18" t="n">
-        <v>7130168</v>
+        <v>7130283</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121492772</v>
+        <v>121492770</v>
       </c>
       <c r="B19" t="n">
-        <v>78607</v>
+        <v>90917</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,25 +2525,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1106</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609974</v>
+        <v>609984</v>
       </c>
       <c r="R19" t="n">
-        <v>7130178</v>
+        <v>7130168</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121492752</v>
+        <v>121492756</v>
       </c>
       <c r="B20" t="n">
-        <v>79717</v>
+        <v>5192</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2635,21 +2635,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609792</v>
+        <v>609843</v>
       </c>
       <c r="R20" t="n">
-        <v>7130369</v>
+        <v>7130300</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121492756</v>
+        <v>121492752</v>
       </c>
       <c r="B21" t="n">
-        <v>5192</v>
+        <v>79717</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609843</v>
+        <v>609792</v>
       </c>
       <c r="R21" t="n">
-        <v>7130300</v>
+        <v>7130369</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2831,10 +2831,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121492757</v>
+        <v>121492755</v>
       </c>
       <c r="B22" t="n">
-        <v>78607</v>
+        <v>90713</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2847,21 +2847,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609889</v>
+        <v>609807</v>
       </c>
       <c r="R22" t="n">
-        <v>7130269</v>
+        <v>7130345</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121492755</v>
+        <v>121492757</v>
       </c>
       <c r="B23" t="n">
-        <v>90713</v>
+        <v>78607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2953,21 +2953,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609807</v>
+        <v>609889</v>
       </c>
       <c r="R23" t="n">
-        <v>7130345</v>
+        <v>7130269</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121492749</v>
+        <v>121492762</v>
       </c>
       <c r="B26" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609806</v>
+        <v>609986</v>
       </c>
       <c r="R26" t="n">
-        <v>7130354</v>
+        <v>7130123</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121492762</v>
+        <v>121492749</v>
       </c>
       <c r="B27" t="n">
-        <v>90731</v>
+        <v>78607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3377,21 +3377,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609986</v>
+        <v>609806</v>
       </c>
       <c r="R27" t="n">
-        <v>7130123</v>
+        <v>7130354</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121492764</v>
+        <v>121492772</v>
       </c>
       <c r="B6" t="n">
-        <v>90731</v>
+        <v>78608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1151,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609989</v>
+        <v>609974</v>
       </c>
       <c r="R6" t="n">
-        <v>7130116</v>
+        <v>7130178</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121492740</v>
+        <v>121492738</v>
       </c>
       <c r="B7" t="n">
-        <v>90731</v>
+        <v>90719</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,21 +1257,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609775</v>
+        <v>609790</v>
       </c>
       <c r="R7" t="n">
-        <v>7130324</v>
+        <v>7130308</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121492747</v>
+        <v>121492761</v>
       </c>
       <c r="B8" t="n">
-        <v>57245</v>
+        <v>57371</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,16 +1363,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609772</v>
+        <v>609958</v>
       </c>
       <c r="R8" t="n">
-        <v>7130374</v>
+        <v>7130181</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121492738</v>
+        <v>121492752</v>
       </c>
       <c r="B9" t="n">
-        <v>90713</v>
+        <v>79718</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,25 +1465,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609790</v>
+        <v>609792</v>
       </c>
       <c r="R9" t="n">
-        <v>7130308</v>
+        <v>7130369</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121492761</v>
+        <v>121492726</v>
       </c>
       <c r="B10" t="n">
-        <v>57370</v>
+        <v>74714</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609958</v>
+        <v>610001</v>
       </c>
       <c r="R10" t="n">
-        <v>7130181</v>
+        <v>7130079</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121492751</v>
+        <v>121492758</v>
       </c>
       <c r="B11" t="n">
-        <v>79648</v>
+        <v>78608</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,25 +1677,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609793</v>
+        <v>609901</v>
       </c>
       <c r="R11" t="n">
-        <v>7130371</v>
+        <v>7130280</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121492769</v>
+        <v>121492754</v>
       </c>
       <c r="B12" t="n">
-        <v>57507</v>
+        <v>78608</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,21 +1787,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609981</v>
+        <v>609790</v>
       </c>
       <c r="R12" t="n">
-        <v>7130145</v>
+        <v>7130365</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121492739</v>
+        <v>121492733</v>
       </c>
       <c r="B13" t="n">
-        <v>97052</v>
+        <v>80565</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1889,25 +1889,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609783</v>
+        <v>609965</v>
       </c>
       <c r="R13" t="n">
-        <v>7130330</v>
+        <v>7130082</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121492754</v>
+        <v>121492768</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>57724</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,25 +1995,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609790</v>
+        <v>609981</v>
       </c>
       <c r="R14" t="n">
-        <v>7130365</v>
+        <v>7130120</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121492726</v>
+        <v>121492746</v>
       </c>
       <c r="B15" t="n">
-        <v>74713</v>
+        <v>78608</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2105,21 +2105,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>610001</v>
+        <v>609772</v>
       </c>
       <c r="R15" t="n">
-        <v>7130079</v>
+        <v>7130393</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121492772</v>
+        <v>121492740</v>
       </c>
       <c r="B16" t="n">
-        <v>78607</v>
+        <v>90737</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609974</v>
+        <v>609775</v>
       </c>
       <c r="R16" t="n">
-        <v>7130178</v>
+        <v>7130324</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121492733</v>
+        <v>121492762</v>
       </c>
       <c r="B17" t="n">
-        <v>80564</v>
+        <v>90737</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2317,21 +2317,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1049</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609965</v>
+        <v>609986</v>
       </c>
       <c r="R17" t="n">
-        <v>7130082</v>
+        <v>7130123</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121492737</v>
+        <v>121492763</v>
       </c>
       <c r="B18" t="n">
-        <v>91369</v>
+        <v>91065</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,21 +2423,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>898</v>
+        <v>2063</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609780</v>
+        <v>609987</v>
       </c>
       <c r="R18" t="n">
-        <v>7130283</v>
+        <v>7130117</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2516,7 +2516,7 @@
         <v>121492770</v>
       </c>
       <c r="B19" t="n">
-        <v>90917</v>
+        <v>90923</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121492756</v>
+        <v>121492769</v>
       </c>
       <c r="B20" t="n">
-        <v>5192</v>
+        <v>57508</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,25 +2631,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609843</v>
+        <v>609981</v>
       </c>
       <c r="R20" t="n">
-        <v>7130300</v>
+        <v>7130145</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121492752</v>
+        <v>121492764</v>
       </c>
       <c r="B21" t="n">
-        <v>79717</v>
+        <v>90737</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2737,25 +2737,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609792</v>
+        <v>609989</v>
       </c>
       <c r="R21" t="n">
-        <v>7130369</v>
+        <v>7130116</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2831,10 +2831,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121492755</v>
+        <v>121492753</v>
       </c>
       <c r="B22" t="n">
-        <v>90713</v>
+        <v>79689</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2847,21 +2847,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609807</v>
+        <v>609794</v>
       </c>
       <c r="R22" t="n">
-        <v>7130345</v>
+        <v>7130370</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121492757</v>
+        <v>121492756</v>
       </c>
       <c r="B23" t="n">
-        <v>78607</v>
+        <v>5192</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2949,25 +2949,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609889</v>
+        <v>609843</v>
       </c>
       <c r="R23" t="n">
-        <v>7130269</v>
+        <v>7130300</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121492763</v>
+        <v>121492739</v>
       </c>
       <c r="B24" t="n">
-        <v>91059</v>
+        <v>97058</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3055,25 +3055,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2063</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609987</v>
+        <v>609783</v>
       </c>
       <c r="R24" t="n">
-        <v>7130117</v>
+        <v>7130330</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3149,10 +3149,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121492771</v>
+        <v>121492747</v>
       </c>
       <c r="B25" t="n">
-        <v>78607</v>
+        <v>57246</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3165,21 +3165,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100001</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609982</v>
+        <v>609772</v>
       </c>
       <c r="R25" t="n">
-        <v>7130159</v>
+        <v>7130374</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121492762</v>
+        <v>121492751</v>
       </c>
       <c r="B26" t="n">
-        <v>90731</v>
+        <v>79649</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3267,25 +3267,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609986</v>
+        <v>609793</v>
       </c>
       <c r="R26" t="n">
-        <v>7130123</v>
+        <v>7130371</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121492749</v>
+        <v>121492759</v>
       </c>
       <c r="B27" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609806</v>
+        <v>609921</v>
       </c>
       <c r="R27" t="n">
-        <v>7130354</v>
+        <v>7130257</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121492768</v>
+        <v>121492749</v>
       </c>
       <c r="B28" t="n">
-        <v>57723</v>
+        <v>78608</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3479,25 +3479,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609981</v>
+        <v>609806</v>
       </c>
       <c r="R28" t="n">
-        <v>7130120</v>
+        <v>7130354</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121492746</v>
+        <v>121492755</v>
       </c>
       <c r="B29" t="n">
-        <v>78607</v>
+        <v>90719</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609772</v>
+        <v>609807</v>
       </c>
       <c r="R29" t="n">
-        <v>7130393</v>
+        <v>7130345</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,10 +3679,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121492753</v>
+        <v>121492757</v>
       </c>
       <c r="B30" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3695,21 +3695,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609794</v>
+        <v>609889</v>
       </c>
       <c r="R30" t="n">
-        <v>7130370</v>
+        <v>7130269</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121492759</v>
+        <v>121492737</v>
       </c>
       <c r="B31" t="n">
-        <v>78607</v>
+        <v>91375</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3797,25 +3797,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609921</v>
+        <v>609780</v>
       </c>
       <c r="R31" t="n">
-        <v>7130257</v>
+        <v>7130283</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121492758</v>
+        <v>121492771</v>
       </c>
       <c r="B32" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609901</v>
+        <v>609982</v>
       </c>
       <c r="R32" t="n">
-        <v>7130280</v>
+        <v>7130159</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121492772</v>
+        <v>121492762</v>
       </c>
       <c r="B6" t="n">
-        <v>78608</v>
+        <v>90738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1151,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609974</v>
+        <v>609986</v>
       </c>
       <c r="R6" t="n">
-        <v>7130178</v>
+        <v>7130123</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121492738</v>
+        <v>121492764</v>
       </c>
       <c r="B7" t="n">
-        <v>90719</v>
+        <v>90738</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,21 +1257,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609790</v>
+        <v>609989</v>
       </c>
       <c r="R7" t="n">
-        <v>7130308</v>
+        <v>7130116</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121492761</v>
+        <v>121492770</v>
       </c>
       <c r="B8" t="n">
-        <v>57371</v>
+        <v>90924</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1106</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609958</v>
+        <v>609984</v>
       </c>
       <c r="R8" t="n">
-        <v>7130181</v>
+        <v>7130168</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121492752</v>
+        <v>121492759</v>
       </c>
       <c r="B9" t="n">
-        <v>79718</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,25 +1465,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609792</v>
+        <v>609921</v>
       </c>
       <c r="R9" t="n">
-        <v>7130369</v>
+        <v>7130257</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121492726</v>
+        <v>121492739</v>
       </c>
       <c r="B10" t="n">
-        <v>74714</v>
+        <v>97059</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,25 +1571,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610001</v>
+        <v>609783</v>
       </c>
       <c r="R10" t="n">
-        <v>7130079</v>
+        <v>7130330</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121492758</v>
+        <v>121492749</v>
       </c>
       <c r="B11" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609901</v>
+        <v>609806</v>
       </c>
       <c r="R11" t="n">
-        <v>7130280</v>
+        <v>7130354</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121492754</v>
+        <v>121492751</v>
       </c>
       <c r="B12" t="n">
-        <v>78608</v>
+        <v>79650</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1783,25 +1783,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609790</v>
+        <v>609793</v>
       </c>
       <c r="R12" t="n">
-        <v>7130365</v>
+        <v>7130371</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121492733</v>
+        <v>121492753</v>
       </c>
       <c r="B13" t="n">
-        <v>80565</v>
+        <v>79690</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1893,21 +1893,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609965</v>
+        <v>609794</v>
       </c>
       <c r="R13" t="n">
-        <v>7130082</v>
+        <v>7130370</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121492768</v>
+        <v>121492771</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,25 +1995,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609981</v>
+        <v>609982</v>
       </c>
       <c r="R14" t="n">
-        <v>7130120</v>
+        <v>7130159</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121492746</v>
+        <v>121492747</v>
       </c>
       <c r="B15" t="n">
-        <v>78608</v>
+        <v>57247</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2105,21 +2105,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100001</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2132,7 +2132,7 @@
         <v>609772</v>
       </c>
       <c r="R15" t="n">
-        <v>7130393</v>
+        <v>7130374</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121492740</v>
+        <v>121492772</v>
       </c>
       <c r="B16" t="n">
-        <v>90737</v>
+        <v>78609</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609775</v>
+        <v>609974</v>
       </c>
       <c r="R16" t="n">
-        <v>7130324</v>
+        <v>7130178</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121492762</v>
+        <v>121492752</v>
       </c>
       <c r="B17" t="n">
-        <v>90737</v>
+        <v>79719</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2313,25 +2313,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609986</v>
+        <v>609792</v>
       </c>
       <c r="R17" t="n">
-        <v>7130123</v>
+        <v>7130369</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121492763</v>
+        <v>121492769</v>
       </c>
       <c r="B18" t="n">
-        <v>91065</v>
+        <v>57509</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2419,25 +2419,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2063</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609987</v>
+        <v>609981</v>
       </c>
       <c r="R18" t="n">
-        <v>7130117</v>
+        <v>7130145</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121492770</v>
+        <v>121492755</v>
       </c>
       <c r="B19" t="n">
-        <v>90923</v>
+        <v>90720</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,25 +2525,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1106</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609984</v>
+        <v>609807</v>
       </c>
       <c r="R19" t="n">
-        <v>7130168</v>
+        <v>7130345</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121492769</v>
+        <v>121492738</v>
       </c>
       <c r="B20" t="n">
-        <v>57508</v>
+        <v>90720</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2635,21 +2635,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609981</v>
+        <v>609790</v>
       </c>
       <c r="R20" t="n">
-        <v>7130145</v>
+        <v>7130308</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121492764</v>
+        <v>121492737</v>
       </c>
       <c r="B21" t="n">
-        <v>90737</v>
+        <v>91376</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2737,25 +2737,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>898</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609989</v>
+        <v>609780</v>
       </c>
       <c r="R21" t="n">
-        <v>7130116</v>
+        <v>7130283</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2831,10 +2831,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121492753</v>
+        <v>121492726</v>
       </c>
       <c r="B22" t="n">
-        <v>79689</v>
+        <v>74715</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2847,21 +2847,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609794</v>
+        <v>610001</v>
       </c>
       <c r="R22" t="n">
-        <v>7130370</v>
+        <v>7130079</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121492756</v>
+        <v>121492758</v>
       </c>
       <c r="B23" t="n">
-        <v>5192</v>
+        <v>78609</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2949,25 +2949,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609843</v>
+        <v>609901</v>
       </c>
       <c r="R23" t="n">
-        <v>7130300</v>
+        <v>7130280</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121492739</v>
+        <v>121492754</v>
       </c>
       <c r="B24" t="n">
-        <v>97058</v>
+        <v>78609</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3055,25 +3055,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609783</v>
+        <v>609790</v>
       </c>
       <c r="R24" t="n">
-        <v>7130330</v>
+        <v>7130365</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3149,10 +3149,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121492747</v>
+        <v>121492756</v>
       </c>
       <c r="B25" t="n">
-        <v>57246</v>
+        <v>5192</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3161,20 +3161,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100001</v>
+        <v>105930</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609772</v>
+        <v>609843</v>
       </c>
       <c r="R25" t="n">
-        <v>7130374</v>
+        <v>7130300</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121492751</v>
+        <v>121492757</v>
       </c>
       <c r="B26" t="n">
-        <v>79649</v>
+        <v>78609</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3267,25 +3267,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609793</v>
+        <v>609889</v>
       </c>
       <c r="R26" t="n">
-        <v>7130371</v>
+        <v>7130269</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121492759</v>
+        <v>121492740</v>
       </c>
       <c r="B27" t="n">
-        <v>78608</v>
+        <v>90738</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3377,21 +3377,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609921</v>
+        <v>609775</v>
       </c>
       <c r="R27" t="n">
-        <v>7130257</v>
+        <v>7130324</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121492749</v>
+        <v>121492768</v>
       </c>
       <c r="B28" t="n">
-        <v>78608</v>
+        <v>57725</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3479,25 +3479,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609806</v>
+        <v>609981</v>
       </c>
       <c r="R28" t="n">
-        <v>7130354</v>
+        <v>7130120</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121492755</v>
+        <v>121492761</v>
       </c>
       <c r="B29" t="n">
-        <v>90719</v>
+        <v>57372</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609807</v>
+        <v>609958</v>
       </c>
       <c r="R29" t="n">
-        <v>7130345</v>
+        <v>7130181</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,10 +3679,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121492757</v>
+        <v>121492733</v>
       </c>
       <c r="B30" t="n">
-        <v>78608</v>
+        <v>80566</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3695,21 +3695,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609889</v>
+        <v>609965</v>
       </c>
       <c r="R30" t="n">
-        <v>7130269</v>
+        <v>7130082</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121492737</v>
+        <v>121492746</v>
       </c>
       <c r="B31" t="n">
-        <v>91375</v>
+        <v>78609</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3797,25 +3797,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>898</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609780</v>
+        <v>609772</v>
       </c>
       <c r="R31" t="n">
-        <v>7130283</v>
+        <v>7130393</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121492771</v>
+        <v>121492763</v>
       </c>
       <c r="B32" t="n">
-        <v>78608</v>
+        <v>91066</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3903,25 +3903,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2063</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609982</v>
+        <v>609987</v>
       </c>
       <c r="R32" t="n">
-        <v>7130159</v>
+        <v>7130117</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121492762</v>
+        <v>121492768</v>
       </c>
       <c r="B6" t="n">
-        <v>90738</v>
+        <v>57725</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,25 +1147,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609986</v>
+        <v>609981</v>
       </c>
       <c r="R6" t="n">
-        <v>7130123</v>
+        <v>7130120</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121492764</v>
+        <v>121492758</v>
       </c>
       <c r="B7" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,21 +1257,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609989</v>
+        <v>609901</v>
       </c>
       <c r="R7" t="n">
-        <v>7130116</v>
+        <v>7130280</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1453,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121492759</v>
+        <v>121492769</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,21 +1469,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609921</v>
+        <v>609981</v>
       </c>
       <c r="R9" t="n">
-        <v>7130257</v>
+        <v>7130145</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121492739</v>
+        <v>121492746</v>
       </c>
       <c r="B10" t="n">
-        <v>97059</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,25 +1571,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609783</v>
+        <v>609772</v>
       </c>
       <c r="R10" t="n">
-        <v>7130330</v>
+        <v>7130393</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121492749</v>
+        <v>121492754</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609806</v>
+        <v>609790</v>
       </c>
       <c r="R11" t="n">
-        <v>7130354</v>
+        <v>7130365</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121492751</v>
+        <v>121492753</v>
       </c>
       <c r="B12" t="n">
-        <v>79650</v>
+        <v>79690</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1783,25 +1783,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609793</v>
+        <v>609794</v>
       </c>
       <c r="R12" t="n">
-        <v>7130371</v>
+        <v>7130370</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121492753</v>
+        <v>121492772</v>
       </c>
       <c r="B13" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1893,21 +1893,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609794</v>
+        <v>609974</v>
       </c>
       <c r="R13" t="n">
-        <v>7130370</v>
+        <v>7130178</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121492771</v>
+        <v>121492764</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,21 +1999,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609982</v>
+        <v>609989</v>
       </c>
       <c r="R14" t="n">
-        <v>7130159</v>
+        <v>7130116</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121492747</v>
+        <v>121492740</v>
       </c>
       <c r="B15" t="n">
-        <v>57247</v>
+        <v>90738</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2105,21 +2105,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100001</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609772</v>
+        <v>609775</v>
       </c>
       <c r="R15" t="n">
-        <v>7130374</v>
+        <v>7130324</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121492772</v>
+        <v>121492733</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>80566</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609974</v>
+        <v>609965</v>
       </c>
       <c r="R16" t="n">
-        <v>7130178</v>
+        <v>7130082</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121492752</v>
+        <v>121492759</v>
       </c>
       <c r="B17" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2313,25 +2313,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609792</v>
+        <v>609921</v>
       </c>
       <c r="R17" t="n">
-        <v>7130369</v>
+        <v>7130257</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121492769</v>
+        <v>121492726</v>
       </c>
       <c r="B18" t="n">
-        <v>57509</v>
+        <v>74715</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,21 +2423,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609981</v>
+        <v>610001</v>
       </c>
       <c r="R18" t="n">
-        <v>7130145</v>
+        <v>7130079</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121492755</v>
+        <v>121492752</v>
       </c>
       <c r="B19" t="n">
-        <v>90720</v>
+        <v>79719</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,25 +2525,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609807</v>
+        <v>609792</v>
       </c>
       <c r="R19" t="n">
-        <v>7130345</v>
+        <v>7130369</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121492738</v>
+        <v>121492751</v>
       </c>
       <c r="B20" t="n">
-        <v>90720</v>
+        <v>79650</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,25 +2631,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609790</v>
+        <v>609793</v>
       </c>
       <c r="R20" t="n">
-        <v>7130308</v>
+        <v>7130371</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121492737</v>
+        <v>121492747</v>
       </c>
       <c r="B21" t="n">
-        <v>91376</v>
+        <v>57247</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2737,25 +2737,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>898</v>
+        <v>100001</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609780</v>
+        <v>609772</v>
       </c>
       <c r="R21" t="n">
-        <v>7130283</v>
+        <v>7130374</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2831,10 +2831,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121492726</v>
+        <v>121492755</v>
       </c>
       <c r="B22" t="n">
-        <v>74715</v>
+        <v>90720</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2847,21 +2847,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>610001</v>
+        <v>609807</v>
       </c>
       <c r="R22" t="n">
-        <v>7130079</v>
+        <v>7130345</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121492758</v>
+        <v>121492739</v>
       </c>
       <c r="B23" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2949,25 +2949,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609901</v>
+        <v>609783</v>
       </c>
       <c r="R23" t="n">
-        <v>7130280</v>
+        <v>7130330</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121492754</v>
+        <v>121492737</v>
       </c>
       <c r="B24" t="n">
-        <v>78609</v>
+        <v>91376</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3055,25 +3055,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609790</v>
+        <v>609780</v>
       </c>
       <c r="R24" t="n">
-        <v>7130365</v>
+        <v>7130283</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3149,10 +3149,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121492756</v>
+        <v>121492749</v>
       </c>
       <c r="B25" t="n">
-        <v>5192</v>
+        <v>78609</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3161,25 +3161,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609843</v>
+        <v>609806</v>
       </c>
       <c r="R25" t="n">
-        <v>7130300</v>
+        <v>7130354</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121492757</v>
+        <v>121492756</v>
       </c>
       <c r="B26" t="n">
-        <v>78609</v>
+        <v>5192</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3267,25 +3267,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609889</v>
+        <v>609843</v>
       </c>
       <c r="R26" t="n">
-        <v>7130269</v>
+        <v>7130300</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,7 +3361,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121492740</v>
+        <v>121492762</v>
       </c>
       <c r="B27" t="n">
         <v>90738</v>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609775</v>
+        <v>609986</v>
       </c>
       <c r="R27" t="n">
-        <v>7130324</v>
+        <v>7130123</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121492768</v>
+        <v>121492763</v>
       </c>
       <c r="B28" t="n">
-        <v>57725</v>
+        <v>91066</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3479,25 +3479,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>2063</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609981</v>
+        <v>609987</v>
       </c>
       <c r="R28" t="n">
-        <v>7130120</v>
+        <v>7130117</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121492761</v>
+        <v>121492771</v>
       </c>
       <c r="B29" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609958</v>
+        <v>609982</v>
       </c>
       <c r="R29" t="n">
-        <v>7130181</v>
+        <v>7130159</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,10 +3679,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121492733</v>
+        <v>121492761</v>
       </c>
       <c r="B30" t="n">
-        <v>80566</v>
+        <v>57372</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3695,21 +3695,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609965</v>
+        <v>609958</v>
       </c>
       <c r="R30" t="n">
-        <v>7130082</v>
+        <v>7130181</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,7 +3785,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121492746</v>
+        <v>121492757</v>
       </c>
       <c r="B31" t="n">
         <v>78609</v>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609772</v>
+        <v>609889</v>
       </c>
       <c r="R31" t="n">
-        <v>7130393</v>
+        <v>7130269</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121492763</v>
+        <v>121492738</v>
       </c>
       <c r="B32" t="n">
-        <v>91066</v>
+        <v>90720</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3903,25 +3903,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2063</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609987</v>
+        <v>609790</v>
       </c>
       <c r="R32" t="n">
-        <v>7130117</v>
+        <v>7130308</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121492768</v>
+        <v>121492761</v>
       </c>
       <c r="B6" t="n">
-        <v>57725</v>
+        <v>57372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,20 +1147,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609981</v>
+        <v>609958</v>
       </c>
       <c r="R6" t="n">
-        <v>7130120</v>
+        <v>7130181</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,7 +1241,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121492758</v>
+        <v>121492772</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609901</v>
+        <v>609974</v>
       </c>
       <c r="R7" t="n">
-        <v>7130280</v>
+        <v>7130178</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121492770</v>
+        <v>121492753</v>
       </c>
       <c r="B8" t="n">
-        <v>90924</v>
+        <v>79690</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1106</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609984</v>
+        <v>609794</v>
       </c>
       <c r="R8" t="n">
-        <v>7130168</v>
+        <v>7130370</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121492769</v>
+        <v>121492762</v>
       </c>
       <c r="B9" t="n">
-        <v>57509</v>
+        <v>90738</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,21 +1469,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609981</v>
+        <v>609986</v>
       </c>
       <c r="R9" t="n">
-        <v>7130145</v>
+        <v>7130123</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121492746</v>
+        <v>121492754</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609772</v>
+        <v>609790</v>
       </c>
       <c r="R10" t="n">
-        <v>7130393</v>
+        <v>7130365</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121492754</v>
+        <v>121492755</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609790</v>
+        <v>609807</v>
       </c>
       <c r="R11" t="n">
-        <v>7130365</v>
+        <v>7130345</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121492753</v>
+        <v>121492759</v>
       </c>
       <c r="B12" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,21 +1787,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609794</v>
+        <v>609921</v>
       </c>
       <c r="R12" t="n">
-        <v>7130370</v>
+        <v>7130257</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121492772</v>
+        <v>121492771</v>
       </c>
       <c r="B13" t="n">
         <v>78609</v>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609974</v>
+        <v>609982</v>
       </c>
       <c r="R13" t="n">
-        <v>7130178</v>
+        <v>7130159</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121492764</v>
+        <v>121492758</v>
       </c>
       <c r="B14" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,21 +1999,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609989</v>
+        <v>609901</v>
       </c>
       <c r="R14" t="n">
-        <v>7130116</v>
+        <v>7130280</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121492740</v>
+        <v>121492739</v>
       </c>
       <c r="B15" t="n">
-        <v>90738</v>
+        <v>97059</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,25 +2101,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609775</v>
+        <v>609783</v>
       </c>
       <c r="R15" t="n">
-        <v>7130324</v>
+        <v>7130330</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121492733</v>
+        <v>121492726</v>
       </c>
       <c r="B16" t="n">
-        <v>80566</v>
+        <v>74715</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609965</v>
+        <v>610001</v>
       </c>
       <c r="R16" t="n">
-        <v>7130082</v>
+        <v>7130079</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121492759</v>
+        <v>121492738</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2317,21 +2317,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609921</v>
+        <v>609790</v>
       </c>
       <c r="R17" t="n">
-        <v>7130257</v>
+        <v>7130308</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121492726</v>
+        <v>121492746</v>
       </c>
       <c r="B18" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,21 +2423,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>610001</v>
+        <v>609772</v>
       </c>
       <c r="R18" t="n">
-        <v>7130079</v>
+        <v>7130393</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121492752</v>
+        <v>121492747</v>
       </c>
       <c r="B19" t="n">
-        <v>79719</v>
+        <v>57247</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,25 +2525,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>100001</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609792</v>
+        <v>609772</v>
       </c>
       <c r="R19" t="n">
-        <v>7130369</v>
+        <v>7130374</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121492751</v>
+        <v>121492749</v>
       </c>
       <c r="B20" t="n">
-        <v>79650</v>
+        <v>78609</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,25 +2631,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609793</v>
+        <v>609806</v>
       </c>
       <c r="R20" t="n">
-        <v>7130371</v>
+        <v>7130354</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121492747</v>
+        <v>121492764</v>
       </c>
       <c r="B21" t="n">
-        <v>57247</v>
+        <v>90738</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100001</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609772</v>
+        <v>609989</v>
       </c>
       <c r="R21" t="n">
-        <v>7130374</v>
+        <v>7130116</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2831,10 +2831,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121492755</v>
+        <v>121492756</v>
       </c>
       <c r="B22" t="n">
-        <v>90720</v>
+        <v>5192</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2843,25 +2843,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609807</v>
+        <v>609843</v>
       </c>
       <c r="R22" t="n">
-        <v>7130345</v>
+        <v>7130300</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121492739</v>
+        <v>121492751</v>
       </c>
       <c r="B23" t="n">
-        <v>97059</v>
+        <v>79650</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2953,21 +2953,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609783</v>
+        <v>609793</v>
       </c>
       <c r="R23" t="n">
-        <v>7130330</v>
+        <v>7130371</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121492737</v>
+        <v>121492757</v>
       </c>
       <c r="B24" t="n">
-        <v>91376</v>
+        <v>78609</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3055,25 +3055,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>898</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609780</v>
+        <v>609889</v>
       </c>
       <c r="R24" t="n">
-        <v>7130283</v>
+        <v>7130269</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3149,10 +3149,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121492749</v>
+        <v>121492763</v>
       </c>
       <c r="B25" t="n">
-        <v>78609</v>
+        <v>91066</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3161,25 +3161,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2063</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609806</v>
+        <v>609987</v>
       </c>
       <c r="R25" t="n">
-        <v>7130354</v>
+        <v>7130117</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121492756</v>
+        <v>121492770</v>
       </c>
       <c r="B26" t="n">
-        <v>5192</v>
+        <v>90924</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3267,25 +3267,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>1106</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609843</v>
+        <v>609984</v>
       </c>
       <c r="R26" t="n">
-        <v>7130300</v>
+        <v>7130168</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,7 +3361,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121492762</v>
+        <v>121492740</v>
       </c>
       <c r="B27" t="n">
         <v>90738</v>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609986</v>
+        <v>609775</v>
       </c>
       <c r="R27" t="n">
-        <v>7130123</v>
+        <v>7130324</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121492763</v>
+        <v>121492752</v>
       </c>
       <c r="B28" t="n">
-        <v>91066</v>
+        <v>79719</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3479,25 +3479,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2063</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609987</v>
+        <v>609792</v>
       </c>
       <c r="R28" t="n">
-        <v>7130117</v>
+        <v>7130369</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121492771</v>
+        <v>121492769</v>
       </c>
       <c r="B29" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609982</v>
+        <v>609981</v>
       </c>
       <c r="R29" t="n">
-        <v>7130159</v>
+        <v>7130145</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,10 +3679,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121492761</v>
+        <v>121492768</v>
       </c>
       <c r="B30" t="n">
-        <v>57372</v>
+        <v>57725</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3691,20 +3691,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609958</v>
+        <v>609981</v>
       </c>
       <c r="R30" t="n">
-        <v>7130181</v>
+        <v>7130120</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121492757</v>
+        <v>121492737</v>
       </c>
       <c r="B31" t="n">
-        <v>78609</v>
+        <v>91376</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3797,25 +3797,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609889</v>
+        <v>609780</v>
       </c>
       <c r="R31" t="n">
-        <v>7130269</v>
+        <v>7130283</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121492738</v>
+        <v>121492733</v>
       </c>
       <c r="B32" t="n">
-        <v>90720</v>
+        <v>80566</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3907,21 +3907,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609790</v>
+        <v>609965</v>
       </c>
       <c r="R32" t="n">
-        <v>7130308</v>
+        <v>7130082</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121492761</v>
+        <v>121492754</v>
       </c>
       <c r="B6" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1151,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609958</v>
+        <v>609790</v>
       </c>
       <c r="R6" t="n">
-        <v>7130181</v>
+        <v>7130365</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,7 +1241,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121492772</v>
+        <v>121492757</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609974</v>
+        <v>609889</v>
       </c>
       <c r="R7" t="n">
-        <v>7130178</v>
+        <v>7130269</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121492753</v>
+        <v>121492759</v>
       </c>
       <c r="B8" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609794</v>
+        <v>609921</v>
       </c>
       <c r="R8" t="n">
-        <v>7130370</v>
+        <v>7130257</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121492762</v>
+        <v>121492771</v>
       </c>
       <c r="B9" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,21 +1469,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609986</v>
+        <v>609982</v>
       </c>
       <c r="R9" t="n">
-        <v>7130123</v>
+        <v>7130159</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121492754</v>
+        <v>121492768</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>57725</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,25 +1571,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609790</v>
+        <v>609981</v>
       </c>
       <c r="R10" t="n">
-        <v>7130365</v>
+        <v>7130120</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121492755</v>
+        <v>121492747</v>
       </c>
       <c r="B11" t="n">
-        <v>90720</v>
+        <v>57247</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609807</v>
+        <v>609772</v>
       </c>
       <c r="R11" t="n">
-        <v>7130345</v>
+        <v>7130374</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1771,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121492759</v>
+        <v>121492749</v>
       </c>
       <c r="B12" t="n">
         <v>78609</v>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609921</v>
+        <v>609806</v>
       </c>
       <c r="R12" t="n">
-        <v>7130257</v>
+        <v>7130354</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121492771</v>
+        <v>121492746</v>
       </c>
       <c r="B13" t="n">
         <v>78609</v>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609982</v>
+        <v>609772</v>
       </c>
       <c r="R13" t="n">
-        <v>7130159</v>
+        <v>7130393</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121492758</v>
+        <v>121492751</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>79650</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,25 +1995,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609901</v>
+        <v>609793</v>
       </c>
       <c r="R14" t="n">
-        <v>7130280</v>
+        <v>7130371</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121492726</v>
+        <v>121492738</v>
       </c>
       <c r="B16" t="n">
-        <v>74715</v>
+        <v>90720</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>610001</v>
+        <v>609790</v>
       </c>
       <c r="R16" t="n">
-        <v>7130079</v>
+        <v>7130308</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121492738</v>
+        <v>121492758</v>
       </c>
       <c r="B17" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2317,21 +2317,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609790</v>
+        <v>609901</v>
       </c>
       <c r="R17" t="n">
-        <v>7130308</v>
+        <v>7130280</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121492746</v>
+        <v>121492753</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,21 +2423,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609772</v>
+        <v>609794</v>
       </c>
       <c r="R18" t="n">
-        <v>7130393</v>
+        <v>7130370</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121492747</v>
+        <v>121492726</v>
       </c>
       <c r="B19" t="n">
-        <v>57247</v>
+        <v>74715</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2529,21 +2529,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100001</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609772</v>
+        <v>610001</v>
       </c>
       <c r="R19" t="n">
-        <v>7130374</v>
+        <v>7130079</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121492749</v>
+        <v>121492763</v>
       </c>
       <c r="B20" t="n">
-        <v>78609</v>
+        <v>91066</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,25 +2631,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2063</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609806</v>
+        <v>609987</v>
       </c>
       <c r="R20" t="n">
-        <v>7130354</v>
+        <v>7130117</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121492764</v>
+        <v>121492770</v>
       </c>
       <c r="B21" t="n">
-        <v>90738</v>
+        <v>90924</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2737,25 +2737,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1106</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609989</v>
+        <v>609984</v>
       </c>
       <c r="R21" t="n">
-        <v>7130116</v>
+        <v>7130168</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121492751</v>
+        <v>121492764</v>
       </c>
       <c r="B23" t="n">
-        <v>79650</v>
+        <v>90738</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2949,25 +2949,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609793</v>
+        <v>609989</v>
       </c>
       <c r="R23" t="n">
-        <v>7130371</v>
+        <v>7130116</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121492757</v>
+        <v>121492733</v>
       </c>
       <c r="B24" t="n">
-        <v>78609</v>
+        <v>80566</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3059,21 +3059,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609889</v>
+        <v>609965</v>
       </c>
       <c r="R24" t="n">
-        <v>7130269</v>
+        <v>7130082</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3149,10 +3149,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121492763</v>
+        <v>121492772</v>
       </c>
       <c r="B25" t="n">
-        <v>91066</v>
+        <v>78609</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3161,25 +3161,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2063</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609987</v>
+        <v>609974</v>
       </c>
       <c r="R25" t="n">
-        <v>7130117</v>
+        <v>7130178</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121492770</v>
+        <v>121492761</v>
       </c>
       <c r="B26" t="n">
-        <v>90924</v>
+        <v>57372</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3267,25 +3267,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1106</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609984</v>
+        <v>609958</v>
       </c>
       <c r="R26" t="n">
-        <v>7130168</v>
+        <v>7130181</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,7 +3361,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121492740</v>
+        <v>121492762</v>
       </c>
       <c r="B27" t="n">
         <v>90738</v>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609775</v>
+        <v>609986</v>
       </c>
       <c r="R27" t="n">
-        <v>7130324</v>
+        <v>7130123</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121492752</v>
+        <v>121492769</v>
       </c>
       <c r="B28" t="n">
-        <v>79719</v>
+        <v>57509</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3479,25 +3479,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609792</v>
+        <v>609981</v>
       </c>
       <c r="R28" t="n">
-        <v>7130369</v>
+        <v>7130145</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121492769</v>
+        <v>121492752</v>
       </c>
       <c r="B29" t="n">
-        <v>57509</v>
+        <v>79719</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3585,25 +3585,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609981</v>
+        <v>609792</v>
       </c>
       <c r="R29" t="n">
-        <v>7130145</v>
+        <v>7130369</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,10 +3679,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121492768</v>
+        <v>121492737</v>
       </c>
       <c r="B30" t="n">
-        <v>57725</v>
+        <v>91376</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3691,25 +3691,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>898</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609981</v>
+        <v>609780</v>
       </c>
       <c r="R30" t="n">
-        <v>7130120</v>
+        <v>7130283</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121492737</v>
+        <v>121492755</v>
       </c>
       <c r="B31" t="n">
-        <v>91376</v>
+        <v>90720</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3797,25 +3797,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609780</v>
+        <v>609807</v>
       </c>
       <c r="R31" t="n">
-        <v>7130283</v>
+        <v>7130345</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121492733</v>
+        <v>121492740</v>
       </c>
       <c r="B32" t="n">
-        <v>80566</v>
+        <v>90738</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3907,21 +3907,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1049</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609965</v>
+        <v>609775</v>
       </c>
       <c r="R32" t="n">
-        <v>7130082</v>
+        <v>7130324</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -2619,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121492763</v>
+        <v>121492770</v>
       </c>
       <c r="B20" t="n">
-        <v>91066</v>
+        <v>90924</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2635,21 +2635,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2063</v>
+        <v>1106</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609987</v>
+        <v>609984</v>
       </c>
       <c r="R20" t="n">
-        <v>7130117</v>
+        <v>7130168</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121492770</v>
+        <v>121492763</v>
       </c>
       <c r="B21" t="n">
-        <v>90924</v>
+        <v>91066</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1106</v>
+        <v>2063</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609984</v>
+        <v>609987</v>
       </c>
       <c r="R21" t="n">
-        <v>7130168</v>
+        <v>7130117</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121492761</v>
+        <v>121492762</v>
       </c>
       <c r="B26" t="n">
-        <v>57372</v>
+        <v>90738</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609958</v>
+        <v>609986</v>
       </c>
       <c r="R26" t="n">
-        <v>7130181</v>
+        <v>7130123</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121492762</v>
+        <v>121492761</v>
       </c>
       <c r="B27" t="n">
-        <v>90738</v>
+        <v>57372</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3377,21 +3377,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609986</v>
+        <v>609958</v>
       </c>
       <c r="R27" t="n">
-        <v>7130123</v>
+        <v>7130181</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121492754</v>
+        <v>121492749</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609790</v>
+        <v>609806</v>
       </c>
       <c r="R6" t="n">
-        <v>7130365</v>
+        <v>7130354</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1244,7 @@
         <v>121492757</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121492759</v>
+        <v>121492758</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609921</v>
+        <v>609901</v>
       </c>
       <c r="R8" t="n">
-        <v>7130257</v>
+        <v>7130280</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121492771</v>
+        <v>121492739</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>97067</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,25 +1465,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609982</v>
+        <v>609783</v>
       </c>
       <c r="R9" t="n">
-        <v>7130159</v>
+        <v>7130330</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121492768</v>
+        <v>121492751</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>79657</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609981</v>
+        <v>609793</v>
       </c>
       <c r="R10" t="n">
-        <v>7130120</v>
+        <v>7130371</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121492747</v>
+        <v>121492756</v>
       </c>
       <c r="B11" t="n">
-        <v>57247</v>
+        <v>5193</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100001</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609772</v>
+        <v>609843</v>
       </c>
       <c r="R11" t="n">
-        <v>7130374</v>
+        <v>7130300</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121492749</v>
+        <v>121492740</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>90746</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,21 +1787,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609806</v>
+        <v>609775</v>
       </c>
       <c r="R12" t="n">
-        <v>7130354</v>
+        <v>7130324</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121492746</v>
+        <v>121492764</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>90746</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1893,21 +1893,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609772</v>
+        <v>609989</v>
       </c>
       <c r="R13" t="n">
-        <v>7130393</v>
+        <v>7130116</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121492751</v>
+        <v>121492747</v>
       </c>
       <c r="B14" t="n">
-        <v>79650</v>
+        <v>57248</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,25 +1995,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>100001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609793</v>
+        <v>609772</v>
       </c>
       <c r="R14" t="n">
-        <v>7130371</v>
+        <v>7130374</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121492739</v>
+        <v>121492763</v>
       </c>
       <c r="B15" t="n">
-        <v>97059</v>
+        <v>91074</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,25 +2101,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>2063</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609783</v>
+        <v>609987</v>
       </c>
       <c r="R15" t="n">
-        <v>7130330</v>
+        <v>7130117</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121492738</v>
+        <v>121492772</v>
       </c>
       <c r="B16" t="n">
-        <v>90720</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609790</v>
+        <v>609974</v>
       </c>
       <c r="R16" t="n">
-        <v>7130308</v>
+        <v>7130178</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121492758</v>
+        <v>121492771</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609901</v>
+        <v>609982</v>
       </c>
       <c r="R17" t="n">
-        <v>7130280</v>
+        <v>7130159</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121492753</v>
+        <v>121492754</v>
       </c>
       <c r="B18" t="n">
-        <v>79690</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,21 +2423,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609794</v>
+        <v>609790</v>
       </c>
       <c r="R18" t="n">
-        <v>7130370</v>
+        <v>7130365</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121492726</v>
+        <v>121492752</v>
       </c>
       <c r="B19" t="n">
-        <v>74715</v>
+        <v>79726</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,25 +2525,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>610001</v>
+        <v>609792</v>
       </c>
       <c r="R19" t="n">
-        <v>7130079</v>
+        <v>7130369</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121492770</v>
+        <v>121492768</v>
       </c>
       <c r="B20" t="n">
-        <v>90924</v>
+        <v>57726</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,25 +2631,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1106</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609984</v>
+        <v>609981</v>
       </c>
       <c r="R20" t="n">
-        <v>7130168</v>
+        <v>7130120</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121492763</v>
+        <v>121492759</v>
       </c>
       <c r="B21" t="n">
-        <v>91066</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2737,25 +2737,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2063</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609987</v>
+        <v>609921</v>
       </c>
       <c r="R21" t="n">
-        <v>7130117</v>
+        <v>7130257</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2831,10 +2831,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121492756</v>
+        <v>121492755</v>
       </c>
       <c r="B22" t="n">
-        <v>5192</v>
+        <v>90728</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2843,25 +2843,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609843</v>
+        <v>609807</v>
       </c>
       <c r="R22" t="n">
-        <v>7130300</v>
+        <v>7130345</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121492764</v>
+        <v>121492762</v>
       </c>
       <c r="B23" t="n">
-        <v>90738</v>
+        <v>90746</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609989</v>
+        <v>609986</v>
       </c>
       <c r="R23" t="n">
-        <v>7130116</v>
+        <v>7130123</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121492733</v>
+        <v>121492753</v>
       </c>
       <c r="B24" t="n">
-        <v>80566</v>
+        <v>79697</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3059,21 +3059,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609965</v>
+        <v>609794</v>
       </c>
       <c r="R24" t="n">
-        <v>7130082</v>
+        <v>7130370</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3149,10 +3149,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121492772</v>
+        <v>121492761</v>
       </c>
       <c r="B25" t="n">
-        <v>78609</v>
+        <v>57373</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3165,21 +3165,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609974</v>
+        <v>609958</v>
       </c>
       <c r="R25" t="n">
-        <v>7130178</v>
+        <v>7130181</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121492762</v>
+        <v>121492769</v>
       </c>
       <c r="B26" t="n">
-        <v>90738</v>
+        <v>57510</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609986</v>
+        <v>609981</v>
       </c>
       <c r="R26" t="n">
-        <v>7130123</v>
+        <v>7130145</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121492761</v>
+        <v>121492770</v>
       </c>
       <c r="B27" t="n">
-        <v>57372</v>
+        <v>90932</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3373,25 +3373,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>1106</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609958</v>
+        <v>609984</v>
       </c>
       <c r="R27" t="n">
-        <v>7130181</v>
+        <v>7130168</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121492769</v>
+        <v>121492733</v>
       </c>
       <c r="B28" t="n">
-        <v>57509</v>
+        <v>80573</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3483,21 +3483,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609981</v>
+        <v>609965</v>
       </c>
       <c r="R28" t="n">
-        <v>7130145</v>
+        <v>7130082</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121492752</v>
+        <v>121492737</v>
       </c>
       <c r="B29" t="n">
-        <v>79719</v>
+        <v>91384</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3585,25 +3585,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>898</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609792</v>
+        <v>609780</v>
       </c>
       <c r="R29" t="n">
-        <v>7130369</v>
+        <v>7130283</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,10 +3679,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121492737</v>
+        <v>121492726</v>
       </c>
       <c r="B30" t="n">
-        <v>91376</v>
+        <v>74722</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3691,25 +3691,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>898</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609780</v>
+        <v>610001</v>
       </c>
       <c r="R30" t="n">
-        <v>7130283</v>
+        <v>7130079</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121492755</v>
+        <v>121492746</v>
       </c>
       <c r="B31" t="n">
-        <v>90720</v>
+        <v>78616</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3801,21 +3801,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609807</v>
+        <v>609772</v>
       </c>
       <c r="R31" t="n">
-        <v>7130345</v>
+        <v>7130393</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121492740</v>
+        <v>121492738</v>
       </c>
       <c r="B32" t="n">
-        <v>90738</v>
+        <v>90728</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3907,21 +3907,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609775</v>
+        <v>609790</v>
       </c>
       <c r="R32" t="n">
-        <v>7130324</v>
+        <v>7130308</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -3361,10 +3361,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121492770</v>
+        <v>121492726</v>
       </c>
       <c r="B27" t="n">
-        <v>90932</v>
+        <v>74722</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3373,25 +3373,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1106</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609984</v>
+        <v>610001</v>
       </c>
       <c r="R27" t="n">
-        <v>7130168</v>
+        <v>7130079</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121492733</v>
+        <v>121492746</v>
       </c>
       <c r="B28" t="n">
-        <v>80573</v>
+        <v>78616</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3483,21 +3483,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609965</v>
+        <v>609772</v>
       </c>
       <c r="R28" t="n">
-        <v>7130082</v>
+        <v>7130393</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121492737</v>
+        <v>121492770</v>
       </c>
       <c r="B29" t="n">
-        <v>91384</v>
+        <v>90932</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>898</v>
+        <v>1106</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609780</v>
+        <v>609984</v>
       </c>
       <c r="R29" t="n">
-        <v>7130283</v>
+        <v>7130168</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,10 +3679,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121492726</v>
+        <v>121492733</v>
       </c>
       <c r="B30" t="n">
-        <v>74722</v>
+        <v>80573</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3695,21 +3695,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>1049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>610001</v>
+        <v>609965</v>
       </c>
       <c r="R30" t="n">
-        <v>7130079</v>
+        <v>7130082</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121492746</v>
+        <v>121492737</v>
       </c>
       <c r="B31" t="n">
-        <v>78616</v>
+        <v>91384</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3797,25 +3797,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609772</v>
+        <v>609780</v>
       </c>
       <c r="R31" t="n">
-        <v>7130393</v>
+        <v>7130283</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121492764</v>
+        <v>121492762</v>
       </c>
       <c r="B6" t="n">
         <v>90746</v>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609989</v>
+        <v>609986</v>
       </c>
       <c r="R6" t="n">
-        <v>7130116</v>
+        <v>7130123</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121492733</v>
+        <v>121492751</v>
       </c>
       <c r="B7" t="n">
-        <v>80573</v>
+        <v>79657</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,25 +1253,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1049</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609965</v>
+        <v>609793</v>
       </c>
       <c r="R7" t="n">
-        <v>7130082</v>
+        <v>7130371</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121492752</v>
+        <v>121492756</v>
       </c>
       <c r="B8" t="n">
-        <v>79726</v>
+        <v>5193</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609792</v>
+        <v>609843</v>
       </c>
       <c r="R8" t="n">
-        <v>7130369</v>
+        <v>7130300</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121492758</v>
+        <v>121492755</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,21 +1469,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609901</v>
+        <v>609807</v>
       </c>
       <c r="R9" t="n">
-        <v>7130280</v>
+        <v>7130345</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121492747</v>
+        <v>121492763</v>
       </c>
       <c r="B10" t="n">
-        <v>57248</v>
+        <v>91074</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,25 +1571,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100001</v>
+        <v>2063</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609772</v>
+        <v>609987</v>
       </c>
       <c r="R10" t="n">
-        <v>7130374</v>
+        <v>7130117</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121492738</v>
+        <v>121492739</v>
       </c>
       <c r="B11" t="n">
-        <v>90728</v>
+        <v>97067</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,25 +1677,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609790</v>
+        <v>609783</v>
       </c>
       <c r="R11" t="n">
-        <v>7130308</v>
+        <v>7130330</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121492739</v>
+        <v>121492769</v>
       </c>
       <c r="B12" t="n">
-        <v>97067</v>
+        <v>57510</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1783,25 +1783,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609783</v>
+        <v>609981</v>
       </c>
       <c r="R12" t="n">
-        <v>7130330</v>
+        <v>7130145</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121492771</v>
+        <v>121492753</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1893,21 +1893,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609982</v>
+        <v>609794</v>
       </c>
       <c r="R13" t="n">
-        <v>7130159</v>
+        <v>7130370</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121492754</v>
+        <v>121492772</v>
       </c>
       <c r="B14" t="n">
         <v>78616</v>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609790</v>
+        <v>609974</v>
       </c>
       <c r="R14" t="n">
-        <v>7130365</v>
+        <v>7130178</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,7 +2089,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121492759</v>
+        <v>121492757</v>
       </c>
       <c r="B15" t="n">
         <v>78616</v>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609921</v>
+        <v>609889</v>
       </c>
       <c r="R15" t="n">
-        <v>7130257</v>
+        <v>7130269</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,7 +2195,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121492757</v>
+        <v>121492759</v>
       </c>
       <c r="B16" t="n">
         <v>78616</v>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609889</v>
+        <v>609921</v>
       </c>
       <c r="R16" t="n">
-        <v>7130269</v>
+        <v>7130257</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121492749</v>
+        <v>121492761</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2317,21 +2317,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609806</v>
+        <v>609958</v>
       </c>
       <c r="R17" t="n">
-        <v>7130354</v>
+        <v>7130181</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121492740</v>
+        <v>121492747</v>
       </c>
       <c r="B19" t="n">
-        <v>90746</v>
+        <v>57248</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2529,21 +2529,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100001</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609775</v>
+        <v>609772</v>
       </c>
       <c r="R19" t="n">
-        <v>7130324</v>
+        <v>7130374</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121492769</v>
+        <v>121492768</v>
       </c>
       <c r="B20" t="n">
-        <v>57510</v>
+        <v>57726</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,25 +2631,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2662,7 +2662,7 @@
         <v>609981</v>
       </c>
       <c r="R20" t="n">
-        <v>7130145</v>
+        <v>7130120</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121492746</v>
+        <v>121492752</v>
       </c>
       <c r="B21" t="n">
-        <v>78616</v>
+        <v>79726</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2737,25 +2737,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609772</v>
+        <v>609792</v>
       </c>
       <c r="R21" t="n">
-        <v>7130393</v>
+        <v>7130369</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2831,10 +2831,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121492753</v>
+        <v>121492749</v>
       </c>
       <c r="B22" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2847,21 +2847,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609794</v>
+        <v>609806</v>
       </c>
       <c r="R22" t="n">
-        <v>7130370</v>
+        <v>7130354</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121492768</v>
+        <v>121492771</v>
       </c>
       <c r="B23" t="n">
-        <v>57726</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2949,25 +2949,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609981</v>
+        <v>609982</v>
       </c>
       <c r="R23" t="n">
-        <v>7130120</v>
+        <v>7130159</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121492726</v>
+        <v>121492758</v>
       </c>
       <c r="B24" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3059,21 +3059,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>610001</v>
+        <v>609901</v>
       </c>
       <c r="R24" t="n">
-        <v>7130079</v>
+        <v>7130280</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3149,10 +3149,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121492770</v>
+        <v>121492726</v>
       </c>
       <c r="B25" t="n">
-        <v>90932</v>
+        <v>74722</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3161,25 +3161,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1106</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609984</v>
+        <v>610001</v>
       </c>
       <c r="R25" t="n">
-        <v>7130168</v>
+        <v>7130079</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121492756</v>
+        <v>121492738</v>
       </c>
       <c r="B26" t="n">
-        <v>5193</v>
+        <v>90728</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3267,25 +3267,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609843</v>
+        <v>609790</v>
       </c>
       <c r="R26" t="n">
-        <v>7130300</v>
+        <v>7130308</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121492763</v>
+        <v>121492740</v>
       </c>
       <c r="B27" t="n">
-        <v>91074</v>
+        <v>90746</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3373,25 +3373,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2063</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609987</v>
+        <v>609775</v>
       </c>
       <c r="R27" t="n">
-        <v>7130117</v>
+        <v>7130324</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,7 +3467,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121492762</v>
+        <v>121492764</v>
       </c>
       <c r="B28" t="n">
         <v>90746</v>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609986</v>
+        <v>609989</v>
       </c>
       <c r="R28" t="n">
-        <v>7130123</v>
+        <v>7130116</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121492761</v>
+        <v>121492746</v>
       </c>
       <c r="B29" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609958</v>
+        <v>609772</v>
       </c>
       <c r="R29" t="n">
-        <v>7130181</v>
+        <v>7130393</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,7 +3679,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121492772</v>
+        <v>121492754</v>
       </c>
       <c r="B30" t="n">
         <v>78616</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609974</v>
+        <v>609790</v>
       </c>
       <c r="R30" t="n">
-        <v>7130178</v>
+        <v>7130365</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121492755</v>
+        <v>121492770</v>
       </c>
       <c r="B31" t="n">
-        <v>90728</v>
+        <v>90932</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3797,25 +3797,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>1106</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609807</v>
+        <v>609984</v>
       </c>
       <c r="R31" t="n">
-        <v>7130345</v>
+        <v>7130168</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121492751</v>
+        <v>121492733</v>
       </c>
       <c r="B32" t="n">
-        <v>79657</v>
+        <v>80573</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3903,25 +3903,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229497</v>
+        <v>1049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609793</v>
+        <v>609965</v>
       </c>
       <c r="R32" t="n">
-        <v>7130371</v>
+        <v>7130082</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -1453,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121492755</v>
+        <v>121492763</v>
       </c>
       <c r="B9" t="n">
-        <v>90728</v>
+        <v>91074</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,25 +1465,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>2063</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609807</v>
+        <v>609987</v>
       </c>
       <c r="R9" t="n">
-        <v>7130345</v>
+        <v>7130117</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121492763</v>
+        <v>121492755</v>
       </c>
       <c r="B10" t="n">
-        <v>91074</v>
+        <v>90728</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,25 +1571,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2063</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609987</v>
+        <v>609807</v>
       </c>
       <c r="R10" t="n">
-        <v>7130117</v>
+        <v>7130345</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121492739</v>
+        <v>121492772</v>
       </c>
       <c r="B11" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,25 +1677,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609783</v>
+        <v>609974</v>
       </c>
       <c r="R11" t="n">
-        <v>7130330</v>
+        <v>7130178</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121492769</v>
+        <v>121492739</v>
       </c>
       <c r="B12" t="n">
-        <v>57510</v>
+        <v>97067</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1783,25 +1783,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609981</v>
+        <v>609783</v>
       </c>
       <c r="R12" t="n">
-        <v>7130145</v>
+        <v>7130330</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121492772</v>
+        <v>121492769</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,21 +1999,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609974</v>
+        <v>609981</v>
       </c>
       <c r="R14" t="n">
-        <v>7130178</v>
+        <v>7130145</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121492737</v>
+        <v>121492747</v>
       </c>
       <c r="B18" t="n">
-        <v>91384</v>
+        <v>57248</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2419,25 +2419,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>898</v>
+        <v>100001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609780</v>
+        <v>609772</v>
       </c>
       <c r="R18" t="n">
-        <v>7130283</v>
+        <v>7130374</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121492747</v>
+        <v>121492737</v>
       </c>
       <c r="B19" t="n">
-        <v>57248</v>
+        <v>91384</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,25 +2525,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100001</v>
+        <v>898</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609772</v>
+        <v>609780</v>
       </c>
       <c r="R19" t="n">
-        <v>7130374</v>
+        <v>7130283</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121492768</v>
+        <v>121492752</v>
       </c>
       <c r="B20" t="n">
-        <v>57726</v>
+        <v>79726</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2635,21 +2635,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609981</v>
+        <v>609792</v>
       </c>
       <c r="R20" t="n">
-        <v>7130120</v>
+        <v>7130369</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121492752</v>
+        <v>121492768</v>
       </c>
       <c r="B21" t="n">
-        <v>79726</v>
+        <v>57726</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609792</v>
+        <v>609981</v>
       </c>
       <c r="R21" t="n">
-        <v>7130369</v>
+        <v>7130120</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121492758</v>
+        <v>121492738</v>
       </c>
       <c r="B24" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3059,21 +3059,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609901</v>
+        <v>609790</v>
       </c>
       <c r="R24" t="n">
-        <v>7130280</v>
+        <v>7130308</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3149,10 +3149,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121492726</v>
+        <v>121492758</v>
       </c>
       <c r="B25" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3165,21 +3165,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>610001</v>
+        <v>609901</v>
       </c>
       <c r="R25" t="n">
-        <v>7130079</v>
+        <v>7130280</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121492738</v>
+        <v>121492726</v>
       </c>
       <c r="B26" t="n">
-        <v>90728</v>
+        <v>74722</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609790</v>
+        <v>610001</v>
       </c>
       <c r="R26" t="n">
-        <v>7130308</v>
+        <v>7130079</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121492762</v>
+        <v>121492769</v>
       </c>
       <c r="B6" t="n">
-        <v>90746</v>
+        <v>57510</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1151,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609986</v>
+        <v>609981</v>
       </c>
       <c r="R6" t="n">
-        <v>7130123</v>
+        <v>7130145</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121492751</v>
+        <v>121492738</v>
       </c>
       <c r="B7" t="n">
-        <v>79657</v>
+        <v>90728</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,25 +1253,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609793</v>
+        <v>609790</v>
       </c>
       <c r="R7" t="n">
-        <v>7130371</v>
+        <v>7130308</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121492756</v>
+        <v>121492755</v>
       </c>
       <c r="B8" t="n">
-        <v>5193</v>
+        <v>90728</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609843</v>
+        <v>609807</v>
       </c>
       <c r="R8" t="n">
-        <v>7130300</v>
+        <v>7130345</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121492763</v>
+        <v>121492768</v>
       </c>
       <c r="B9" t="n">
-        <v>91074</v>
+        <v>57726</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,25 +1465,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2063</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609987</v>
+        <v>609981</v>
       </c>
       <c r="R9" t="n">
-        <v>7130117</v>
+        <v>7130120</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121492755</v>
+        <v>121492756</v>
       </c>
       <c r="B10" t="n">
-        <v>90728</v>
+        <v>5193</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,25 +1571,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609807</v>
+        <v>609843</v>
       </c>
       <c r="R10" t="n">
-        <v>7130345</v>
+        <v>7130300</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121492772</v>
+        <v>121492759</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609974</v>
+        <v>609921</v>
       </c>
       <c r="R11" t="n">
-        <v>7130178</v>
+        <v>7130257</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121492739</v>
+        <v>121492746</v>
       </c>
       <c r="B12" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1783,25 +1783,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609783</v>
+        <v>609772</v>
       </c>
       <c r="R12" t="n">
-        <v>7130330</v>
+        <v>7130393</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121492753</v>
+        <v>121492772</v>
       </c>
       <c r="B13" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1893,21 +1893,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609794</v>
+        <v>609974</v>
       </c>
       <c r="R13" t="n">
-        <v>7130370</v>
+        <v>7130178</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121492769</v>
+        <v>121492753</v>
       </c>
       <c r="B14" t="n">
-        <v>57510</v>
+        <v>79697</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,21 +1999,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609981</v>
+        <v>609794</v>
       </c>
       <c r="R14" t="n">
-        <v>7130145</v>
+        <v>7130370</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121492757</v>
+        <v>121492764</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2105,21 +2105,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609889</v>
+        <v>609989</v>
       </c>
       <c r="R15" t="n">
-        <v>7130269</v>
+        <v>7130116</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121492759</v>
+        <v>121492763</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
+        <v>91074</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2207,25 +2207,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2063</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609921</v>
+        <v>609987</v>
       </c>
       <c r="R16" t="n">
-        <v>7130257</v>
+        <v>7130117</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121492761</v>
+        <v>121492752</v>
       </c>
       <c r="B17" t="n">
-        <v>57373</v>
+        <v>79726</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2313,25 +2313,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609958</v>
+        <v>609792</v>
       </c>
       <c r="R17" t="n">
-        <v>7130181</v>
+        <v>7130369</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121492747</v>
+        <v>121492740</v>
       </c>
       <c r="B18" t="n">
-        <v>57248</v>
+        <v>90746</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,21 +2423,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100001</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609772</v>
+        <v>609775</v>
       </c>
       <c r="R18" t="n">
-        <v>7130374</v>
+        <v>7130324</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121492737</v>
+        <v>121492757</v>
       </c>
       <c r="B19" t="n">
-        <v>91384</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,25 +2525,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>898</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609780</v>
+        <v>609889</v>
       </c>
       <c r="R19" t="n">
-        <v>7130283</v>
+        <v>7130269</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121492752</v>
+        <v>121492771</v>
       </c>
       <c r="B20" t="n">
-        <v>79726</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,25 +2631,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609792</v>
+        <v>609982</v>
       </c>
       <c r="R20" t="n">
-        <v>7130369</v>
+        <v>7130159</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121492768</v>
+        <v>121492733</v>
       </c>
       <c r="B21" t="n">
-        <v>57726</v>
+        <v>80573</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2737,25 +2737,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>1049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609981</v>
+        <v>609965</v>
       </c>
       <c r="R21" t="n">
-        <v>7130120</v>
+        <v>7130082</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2831,10 +2831,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121492749</v>
+        <v>121492726</v>
       </c>
       <c r="B22" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2847,21 +2847,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609806</v>
+        <v>610001</v>
       </c>
       <c r="R22" t="n">
-        <v>7130354</v>
+        <v>7130079</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121492771</v>
+        <v>121492751</v>
       </c>
       <c r="B23" t="n">
-        <v>78616</v>
+        <v>79657</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2949,25 +2949,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609982</v>
+        <v>609793</v>
       </c>
       <c r="R23" t="n">
-        <v>7130159</v>
+        <v>7130371</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121492738</v>
+        <v>121492758</v>
       </c>
       <c r="B24" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3059,21 +3059,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609790</v>
+        <v>609901</v>
       </c>
       <c r="R24" t="n">
-        <v>7130308</v>
+        <v>7130280</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3149,10 +3149,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121492758</v>
+        <v>121492737</v>
       </c>
       <c r="B25" t="n">
-        <v>78616</v>
+        <v>91384</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3161,25 +3161,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609901</v>
+        <v>609780</v>
       </c>
       <c r="R25" t="n">
-        <v>7130280</v>
+        <v>7130283</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121492726</v>
+        <v>121492747</v>
       </c>
       <c r="B26" t="n">
-        <v>74722</v>
+        <v>57248</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>100001</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>610001</v>
+        <v>609772</v>
       </c>
       <c r="R26" t="n">
-        <v>7130079</v>
+        <v>7130374</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121492740</v>
+        <v>121492770</v>
       </c>
       <c r="B27" t="n">
-        <v>90746</v>
+        <v>90932</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3373,25 +3373,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1106</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609775</v>
+        <v>609984</v>
       </c>
       <c r="R27" t="n">
-        <v>7130324</v>
+        <v>7130168</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121492764</v>
+        <v>121492749</v>
       </c>
       <c r="B28" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3483,21 +3483,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609989</v>
+        <v>609806</v>
       </c>
       <c r="R28" t="n">
-        <v>7130116</v>
+        <v>7130354</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121492746</v>
+        <v>121492762</v>
       </c>
       <c r="B29" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609772</v>
+        <v>609986</v>
       </c>
       <c r="R29" t="n">
-        <v>7130393</v>
+        <v>7130123</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,10 +3679,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121492754</v>
+        <v>121492761</v>
       </c>
       <c r="B30" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3695,21 +3695,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609790</v>
+        <v>609958</v>
       </c>
       <c r="R30" t="n">
-        <v>7130365</v>
+        <v>7130181</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121492770</v>
+        <v>121492739</v>
       </c>
       <c r="B31" t="n">
-        <v>90932</v>
+        <v>97067</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3797,25 +3797,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1106</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609984</v>
+        <v>609783</v>
       </c>
       <c r="R31" t="n">
-        <v>7130168</v>
+        <v>7130330</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121492733</v>
+        <v>121492754</v>
       </c>
       <c r="B32" t="n">
-        <v>80573</v>
+        <v>78616</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3907,21 +3907,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609965</v>
+        <v>609790</v>
       </c>
       <c r="R32" t="n">
-        <v>7130082</v>
+        <v>7130365</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121492756</v>
+        <v>121492759</v>
       </c>
       <c r="B10" t="n">
-        <v>5193</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,25 +1571,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609843</v>
+        <v>609921</v>
       </c>
       <c r="R10" t="n">
-        <v>7130300</v>
+        <v>7130257</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121492759</v>
+        <v>121492746</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609921</v>
+        <v>609772</v>
       </c>
       <c r="R11" t="n">
-        <v>7130257</v>
+        <v>7130393</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1771,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121492746</v>
+        <v>121492772</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609772</v>
+        <v>609974</v>
       </c>
       <c r="R12" t="n">
-        <v>7130393</v>
+        <v>7130178</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121492772</v>
+        <v>121492756</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>5193</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1889,25 +1889,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609974</v>
+        <v>609843</v>
       </c>
       <c r="R13" t="n">
-        <v>7130178</v>
+        <v>7130300</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121492762</v>
+        <v>121492761</v>
       </c>
       <c r="B29" t="n">
-        <v>90746</v>
+        <v>57373</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609986</v>
+        <v>609958</v>
       </c>
       <c r="R29" t="n">
-        <v>7130123</v>
+        <v>7130181</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,10 +3679,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121492761</v>
+        <v>121492762</v>
       </c>
       <c r="B30" t="n">
-        <v>57373</v>
+        <v>90746</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3695,21 +3695,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609958</v>
+        <v>609986</v>
       </c>
       <c r="R30" t="n">
-        <v>7130181</v>
+        <v>7130123</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 32121-2022 artfynd.xlsx
+++ b/artfynd/A 32121-2022 artfynd.xlsx
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121492769</v>
+        <v>121492762</v>
       </c>
       <c r="B6" t="n">
-        <v>57510</v>
+        <v>90746</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1151,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609981</v>
+        <v>609986</v>
       </c>
       <c r="R6" t="n">
-        <v>7130145</v>
+        <v>7130123</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121492738</v>
+        <v>121492764</v>
       </c>
       <c r="B7" t="n">
-        <v>90728</v>
+        <v>90746</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,21 +1257,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609790</v>
+        <v>609989</v>
       </c>
       <c r="R7" t="n">
-        <v>7130308</v>
+        <v>7130116</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121492755</v>
+        <v>121492737</v>
       </c>
       <c r="B8" t="n">
-        <v>90728</v>
+        <v>91384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609807</v>
+        <v>609780</v>
       </c>
       <c r="R8" t="n">
-        <v>7130345</v>
+        <v>7130283</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121492768</v>
+        <v>121492770</v>
       </c>
       <c r="B9" t="n">
-        <v>57726</v>
+        <v>90932</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,25 +1465,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>1106</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609981</v>
+        <v>609984</v>
       </c>
       <c r="R9" t="n">
-        <v>7130120</v>
+        <v>7130168</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121492759</v>
+        <v>121492739</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,25 +1571,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609921</v>
+        <v>609783</v>
       </c>
       <c r="R10" t="n">
-        <v>7130257</v>
+        <v>7130330</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121492746</v>
+        <v>121492751</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>79657</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,25 +1677,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609772</v>
+        <v>609793</v>
       </c>
       <c r="R11" t="n">
-        <v>7130393</v>
+        <v>7130371</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121492756</v>
+        <v>121492753</v>
       </c>
       <c r="B13" t="n">
-        <v>5193</v>
+        <v>79697</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1889,25 +1889,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609843</v>
+        <v>609794</v>
       </c>
       <c r="R13" t="n">
-        <v>7130300</v>
+        <v>7130370</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121492753</v>
+        <v>121492769</v>
       </c>
       <c r="B14" t="n">
-        <v>79697</v>
+        <v>57510</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,21 +1999,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609794</v>
+        <v>609981</v>
       </c>
       <c r="R14" t="n">
-        <v>7130370</v>
+        <v>7130145</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121492764</v>
+        <v>121492733</v>
       </c>
       <c r="B15" t="n">
-        <v>90746</v>
+        <v>80573</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2105,21 +2105,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609989</v>
+        <v>609965</v>
       </c>
       <c r="R15" t="n">
-        <v>7130116</v>
+        <v>7130082</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121492763</v>
+        <v>121492759</v>
       </c>
       <c r="B16" t="n">
-        <v>91074</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2207,25 +2207,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2063</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609987</v>
+        <v>609921</v>
       </c>
       <c r="R16" t="n">
-        <v>7130117</v>
+        <v>7130257</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121492752</v>
+        <v>121492763</v>
       </c>
       <c r="B17" t="n">
-        <v>79726</v>
+        <v>91074</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2313,25 +2313,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>2063</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609792</v>
+        <v>609987</v>
       </c>
       <c r="R17" t="n">
-        <v>7130369</v>
+        <v>7130117</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121492740</v>
+        <v>121492757</v>
       </c>
       <c r="B18" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,21 +2423,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609775</v>
+        <v>609889</v>
       </c>
       <c r="R18" t="n">
-        <v>7130324</v>
+        <v>7130269</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,7 +2513,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121492757</v>
+        <v>121492771</v>
       </c>
       <c r="B19" t="n">
         <v>78616</v>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609889</v>
+        <v>609982</v>
       </c>
       <c r="R19" t="n">
-        <v>7130269</v>
+        <v>7130159</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,7 +2619,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121492771</v>
+        <v>121492746</v>
       </c>
       <c r="B20" t="n">
         <v>78616</v>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609982</v>
+        <v>609772</v>
       </c>
       <c r="R20" t="n">
-        <v>7130159</v>
+        <v>7130393</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121492733</v>
+        <v>121492756</v>
       </c>
       <c r="B21" t="n">
-        <v>80573</v>
+        <v>5193</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2737,25 +2737,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609965</v>
+        <v>609843</v>
       </c>
       <c r="R21" t="n">
-        <v>7130082</v>
+        <v>7130300</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2831,10 +2831,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121492726</v>
+        <v>121492747</v>
       </c>
       <c r="B22" t="n">
-        <v>74722</v>
+        <v>57248</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2847,21 +2847,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>100001</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>610001</v>
+        <v>609772</v>
       </c>
       <c r="R22" t="n">
-        <v>7130079</v>
+        <v>7130374</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121492751</v>
+        <v>121492738</v>
       </c>
       <c r="B23" t="n">
-        <v>79657</v>
+        <v>90728</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2949,25 +2949,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609793</v>
+        <v>609790</v>
       </c>
       <c r="R23" t="n">
-        <v>7130371</v>
+        <v>7130308</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3149,10 +3149,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121492737</v>
+        <v>121492749</v>
       </c>
       <c r="B25" t="n">
-        <v>91384</v>
+        <v>78616</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3161,25 +3161,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>898</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609780</v>
+        <v>609806</v>
       </c>
       <c r="R25" t="n">
-        <v>7130283</v>
+        <v>7130354</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121492747</v>
+        <v>121492740</v>
       </c>
       <c r="B26" t="n">
-        <v>57248</v>
+        <v>90746</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100001</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609772</v>
+        <v>609775</v>
       </c>
       <c r="R26" t="n">
-        <v>7130374</v>
+        <v>7130324</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121492770</v>
+        <v>121492726</v>
       </c>
       <c r="B27" t="n">
-        <v>90932</v>
+        <v>74722</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3373,25 +3373,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1106</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609984</v>
+        <v>610001</v>
       </c>
       <c r="R27" t="n">
-        <v>7130168</v>
+        <v>7130079</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121492749</v>
+        <v>121492768</v>
       </c>
       <c r="B28" t="n">
-        <v>78616</v>
+        <v>57726</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3479,25 +3479,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609806</v>
+        <v>609981</v>
       </c>
       <c r="R28" t="n">
-        <v>7130354</v>
+        <v>7130120</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121492761</v>
+        <v>121492755</v>
       </c>
       <c r="B29" t="n">
-        <v>57373</v>
+        <v>90728</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609958</v>
+        <v>609807</v>
       </c>
       <c r="R29" t="n">
-        <v>7130181</v>
+        <v>7130345</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,10 +3679,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121492762</v>
+        <v>121492752</v>
       </c>
       <c r="B30" t="n">
-        <v>90746</v>
+        <v>79726</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3691,25 +3691,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609986</v>
+        <v>609792</v>
       </c>
       <c r="R30" t="n">
-        <v>7130123</v>
+        <v>7130369</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121492739</v>
+        <v>121492761</v>
       </c>
       <c r="B31" t="n">
-        <v>97067</v>
+        <v>57373</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3797,25 +3797,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609783</v>
+        <v>609958</v>
       </c>
       <c r="R31" t="n">
-        <v>7130330</v>
+        <v>7130181</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
